--- a/dataExport/作品列表导出.xlsx
+++ b/dataExport/作品列表导出.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
   <si>
     <t>作品名称</t>
   </si>
@@ -64,6 +64,162 @@
   </si>
   <si>
     <t>粉丝增量</t>
+  </si>
+  <si>
+    <t>决明子：又名草决明 《神农本草经》卷一·上经载决明子。
+  本片照录原文，逐句今译，并说明「青盲」「白膜」在汉代指什么。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-01 19:00:00</t>
+  </si>
+  <si>
+    <t>1min-视频</t>
+  </si>
+  <si>
+    <t>公开</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>0.112142</t>
+  </si>
+  <si>
+    <t>0.399072</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.235112</t>
+  </si>
+  <si>
+    <t>10.778036</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>防风：古书说的「大风」是什么 《神农本草经》卷一·上经载防风。
+  本片照录原文，逐句今译，并说明「大风」「痹」在汉代指什么。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-01 08:00:00</t>
+  </si>
+  <si>
+    <t>689</t>
+  </si>
+  <si>
+    <t>0.044140</t>
+  </si>
+  <si>
+    <t>0.241679</t>
+  </si>
+  <si>
+    <t>0.429812</t>
+  </si>
+  <si>
+    <t>5.342981</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>蓝实：古书里的染青草 《神农本草经》卷一·上经载蓝实。
+  本片照录原文，逐句今译，并说明「蛊」「注鬼」是汉代的病名观念。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-09-30 19:00:00</t>
+  </si>
+  <si>
+    <t>708</t>
+  </si>
+  <si>
+    <t>0.092414</t>
+  </si>
+  <si>
+    <t>0.283444</t>
+  </si>
+  <si>
+    <t>0.324503</t>
+  </si>
+  <si>
+    <t>6.480795</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>紫芝：六芝之一，色紫如桑 《神农本草经》卷一·上经载紫芝。
+  本片照录原文，逐句今译，并说明「保神」「好颜色」在汉代是什么意思。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍古书  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-09-30 08:00:00</t>
+  </si>
+  <si>
+    <t>1863</t>
+  </si>
+  <si>
+    <t>0.062771</t>
+  </si>
+  <si>
+    <t>0.343880</t>
+  </si>
+  <si>
+    <t>0.241183</t>
+  </si>
+  <si>
+    <t>7.210062</t>
+  </si>
+  <si>
+    <t>黄芝：古书说它黄如紫金 《神农本草经》卷一·上经载黄芝。
+本片照录原文，逐句今译，附注释说明，并配灵芝照片（Ganoderma curtisii）。
+古籍内容展示，不构成诊疗建议。
+#黄芝  #神农本草经  #中医  #中草药 #中药材</t>
+  </si>
+  <si>
+    <t>2026-09-27 19:19:09</t>
+  </si>
+  <si>
+    <t>1667</t>
+  </si>
+  <si>
+    <t>0.067463</t>
+  </si>
+  <si>
+    <t>0.323569</t>
+  </si>
+  <si>
+    <t>0.209128</t>
+  </si>
+  <si>
+    <t>6.051090</t>
   </si>
   <si>
     <t>白芝：入肺应秋的玉芝 《神农本草经》卷一上经的白芝：味辛平，主咳逆上气、益肺气、通利口鼻、安魄。
@@ -75,43 +231,28 @@
     <t>2026-09-25 08:00:00</t>
   </si>
   <si>
-    <t>1min-视频</t>
-  </si>
-  <si>
-    <t>公开</t>
-  </si>
-  <si>
-    <t>1944</t>
-  </si>
-  <si>
-    <t>0.139808</t>
-  </si>
-  <si>
-    <t>0.345390</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.270504</t>
-  </si>
-  <si>
-    <t>6.700458</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>1961</t>
+  </si>
+  <si>
+    <t>0.140010</t>
+  </si>
+  <si>
+    <t>0.343812</t>
+  </si>
+  <si>
+    <t>0.273453</t>
+  </si>
+  <si>
+    <t>6.667665</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
     <t>11</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>青芝：入肝应春的明目芝 《神农本草经》卷一上经的青芝：味酸平，主明目、补肝气、安精魂。
@@ -123,34 +264,22 @@
     <t>2026-09-24 19:00:00</t>
   </si>
   <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>0.127014</t>
-  </si>
-  <si>
-    <t>0.298043</t>
-  </si>
-  <si>
-    <t>0.320285</t>
-  </si>
-  <si>
-    <t>6.495552</t>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>0.125693</t>
+  </si>
+  <si>
+    <t>0.294271</t>
+  </si>
+  <si>
+    <t>0.317708</t>
+  </si>
+  <si>
+    <t>6.446181</t>
   </si>
   <si>
     <t>13</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>赤芝：六芝之首的安神上品 《神农本草经》卷一上经的赤芝：味苦平，益心气、补中、增智慧、不忘。
@@ -162,19 +291,19 @@
     <t>2026-09-24 08:00:00</t>
   </si>
   <si>
-    <t>2950</t>
-  </si>
-  <si>
-    <t>0.111416</t>
-  </si>
-  <si>
-    <t>0.307897</t>
-  </si>
-  <si>
-    <t>0.284531</t>
-  </si>
-  <si>
-    <t>5.902100</t>
+    <t>2961</t>
+  </si>
+  <si>
+    <t>0.113001</t>
+  </si>
+  <si>
+    <t>0.309293</t>
+  </si>
+  <si>
+    <t>0.283788</t>
+  </si>
+  <si>
+    <t>5.912049</t>
   </si>
   <si>
     <t>10</t>
@@ -192,19 +321,22 @@
     <t>2026-09-23 20:00:00</t>
   </si>
   <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>0.183511</t>
-  </si>
-  <si>
-    <t>0.421227</t>
-  </si>
-  <si>
-    <t>0.228027</t>
-  </si>
-  <si>
-    <t>6.970149</t>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>0.188215</t>
+  </si>
+  <si>
+    <t>0.422824</t>
+  </si>
+  <si>
+    <t>0.226601</t>
+  </si>
+  <si>
+    <t>6.987685</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>奄闾子：食之神仙的蒿类 《神农本草经》卷一上经的奄闾子：味苦微寒，主五脏瘀血、腹中水气、身体诸痛。
@@ -216,22 +348,19 @@
     <t>2026-09-23 08:00:00</t>
   </si>
   <si>
-    <t>783</t>
-  </si>
-  <si>
-    <t>0.176556</t>
-  </si>
-  <si>
-    <t>0.440655</t>
-  </si>
-  <si>
-    <t>0.251023</t>
-  </si>
-  <si>
-    <t>8.118690</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>793</t>
+  </si>
+  <si>
+    <t>0.174037</t>
+  </si>
+  <si>
+    <t>0.433962</t>
+  </si>
+  <si>
+    <t>0.253369</t>
+  </si>
+  <si>
+    <t>8.045760</t>
   </si>
   <si>
     <t>析子：俗呼老荠的明目药 《神农本草经》卷一上经的析子（菥蓂）：味辛微温，主目痛泪出、益精光。
@@ -243,25 +372,19 @@
     <t>2026-09-22 20:00:00</t>
   </si>
   <si>
-    <t>664</t>
-  </si>
-  <si>
-    <t>0.148611</t>
-  </si>
-  <si>
-    <t>0.370565</t>
-  </si>
-  <si>
-    <t>0.252300</t>
-  </si>
-  <si>
-    <t>8.708279</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>667</t>
+  </si>
+  <si>
+    <t>0.147994</t>
+  </si>
+  <si>
+    <t>0.370904</t>
+  </si>
+  <si>
+    <t>0.251638</t>
+  </si>
+  <si>
+    <t>8.705111</t>
   </si>
   <si>
     <t>赤箭：其实就是天麻 《神农本草经》卷一上经的赤箭：味辛温，主杀鬼精物蛊毒恶气，久服增年。
@@ -273,22 +396,19 @@
     <t>2026-09-22 08:00:00</t>
   </si>
   <si>
-    <t>1899</t>
-  </si>
-  <si>
-    <t>0.152000</t>
-  </si>
-  <si>
-    <t>0.377130</t>
-  </si>
-  <si>
-    <t>0.220628</t>
-  </si>
-  <si>
-    <t>8.162332</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>0.151572</t>
+  </si>
+  <si>
+    <t>0.376118</t>
+  </si>
+  <si>
+    <t>0.220930</t>
+  </si>
+  <si>
+    <t>8.146691</t>
   </si>
   <si>
     <t>白蒿：《诗经》里的采蘩 《神农本草经》卷一上经的白蒿：味甘平，补中益气，长毛发令黑，疗心悬。
@@ -300,19 +420,19 @@
     <t>2026-09-21 19:00:00</t>
   </si>
   <si>
-    <t>1964</t>
-  </si>
-  <si>
-    <t>0.120995</t>
-  </si>
-  <si>
-    <t>0.331504</t>
-  </si>
-  <si>
-    <t>0.256516</t>
-  </si>
-  <si>
-    <t>5.891175</t>
+    <t>1968</t>
+  </si>
+  <si>
+    <t>0.120821</t>
+  </si>
+  <si>
+    <t>0.331050</t>
+  </si>
+  <si>
+    <t>0.256164</t>
+  </si>
+  <si>
+    <t>5.887215</t>
   </si>
   <si>
     <t>14</t>
@@ -327,19 +447,19 @@
     <t>2026-09-21 08:00:00</t>
   </si>
   <si>
-    <t>2945</t>
-  </si>
-  <si>
-    <t>0.164363</t>
-  </si>
-  <si>
-    <t>0.383844</t>
-  </si>
-  <si>
-    <t>0.240905</t>
-  </si>
-  <si>
-    <t>8.939559</t>
+    <t>2948</t>
+  </si>
+  <si>
+    <t>0.164314</t>
+  </si>
+  <si>
+    <t>0.384197</t>
+  </si>
+  <si>
+    <t>0.240767</t>
+  </si>
+  <si>
+    <t>8.964787</t>
   </si>
   <si>
     <t>17</t>
@@ -354,19 +474,19 @@
     <t>2026-09-20 19:00:00</t>
   </si>
   <si>
-    <t>3016</t>
-  </si>
-  <si>
-    <t>0.188143</t>
-  </si>
-  <si>
-    <t>0.426230</t>
-  </si>
-  <si>
-    <t>0.223019</t>
-  </si>
-  <si>
-    <t>7.623634</t>
+    <t>3018</t>
+  </si>
+  <si>
+    <t>0.188077</t>
+  </si>
+  <si>
+    <t>0.426425</t>
+  </si>
+  <si>
+    <t>0.222943</t>
+  </si>
+  <si>
+    <t>7.624445</t>
   </si>
   <si>
     <t>20</t>
@@ -381,19 +501,19 @@
     <t>2026-09-20 14:08:36</t>
   </si>
   <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>0.152244</t>
-  </si>
-  <si>
-    <t>0.380090</t>
-  </si>
-  <si>
-    <t>0.251885</t>
-  </si>
-  <si>
-    <t>7.334842</t>
+    <t>585</t>
+  </si>
+  <si>
+    <t>0.152000</t>
+  </si>
+  <si>
+    <t>0.381024</t>
+  </si>
+  <si>
+    <t>0.251506</t>
+  </si>
+  <si>
+    <t>7.335843</t>
   </si>
   <si>
     <t>细辛：华阴色白者为善 《神农本草经》卷一上经的细辛：味辛温，主头痛脑动、百节拘挛、风湿痹痛。
@@ -405,19 +525,19 @@
     <t>2026-09-19 19:00:00</t>
   </si>
   <si>
-    <t>1374</t>
-  </si>
-  <si>
-    <t>0.108819</t>
-  </si>
-  <si>
-    <t>0.299046</t>
-  </si>
-  <si>
-    <t>0.353542</t>
-  </si>
-  <si>
-    <t>5.698910</t>
+    <t>1376</t>
+  </si>
+  <si>
+    <t>0.109453</t>
+  </si>
+  <si>
+    <t>0.299523</t>
+  </si>
+  <si>
+    <t>0.353302</t>
+  </si>
+  <si>
+    <t>5.703880</t>
   </si>
   <si>
     <t>龙胆：主骨间寒热的苦口上品 《神农本草经》卷一上经的龙胆：味苦涩，主惊痫邪气、续绝伤、杀蛊毒。
@@ -429,19 +549,22 @@
     <t>2026-09-19 08:00:00</t>
   </si>
   <si>
-    <t>2967</t>
-  </si>
-  <si>
-    <t>0.149035</t>
-  </si>
-  <si>
-    <t>0.364213</t>
-  </si>
-  <si>
-    <t>0.269670</t>
-  </si>
-  <si>
-    <t>7.196383</t>
+    <t>2977</t>
+  </si>
+  <si>
+    <t>0.149070</t>
+  </si>
+  <si>
+    <t>0.364557</t>
+  </si>
+  <si>
+    <t>0.269620</t>
+  </si>
+  <si>
+    <t>7.194304</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>远志：它的叶子叫小草 《神农本草经》卷一上经的远志：味苦温，利九窍、益智慧、不忘、强志倍力。
@@ -453,22 +576,19 @@
     <t>2026-09-18 19:00:00</t>
   </si>
   <si>
-    <t>1948</t>
-  </si>
-  <si>
-    <t>0.128244</t>
-  </si>
-  <si>
-    <t>0.306888</t>
-  </si>
-  <si>
-    <t>0.327791</t>
-  </si>
-  <si>
-    <t>6.136817</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>1959</t>
+  </si>
+  <si>
+    <t>0.127797</t>
+  </si>
+  <si>
+    <t>0.306818</t>
+  </si>
+  <si>
+    <t>0.329072</t>
+  </si>
+  <si>
+    <t>6.126894</t>
   </si>
   <si>
     <t>泽泻：能行水上的本经奇谈 《神农本草经》卷一上经的泽泻：味甘寒，主风寒湿痹、乳难，消水养五脏。
@@ -480,19 +600,19 @@
     <t>2026-09-18 08:00:00</t>
   </si>
   <si>
-    <t>2791</t>
-  </si>
-  <si>
-    <t>0.145999</t>
-  </si>
-  <si>
-    <t>0.364489</t>
-  </si>
-  <si>
-    <t>0.238500</t>
-  </si>
-  <si>
-    <t>7.506885</t>
+    <t>2800</t>
+  </si>
+  <si>
+    <t>0.145910</t>
+  </si>
+  <si>
+    <t>0.364275</t>
+  </si>
+  <si>
+    <t>0.238360</t>
+  </si>
+  <si>
+    <t>7.504246</t>
   </si>
   <si>
     <t>薏苡仁：马援常饵的轻身药 《神农本草经》卷一上经的薏苡仁：味甘微寒，主拘挛不可屈伸、风湿痹、下气。
@@ -504,19 +624,19 @@
     <t>2026-09-17 19:00:00</t>
   </si>
   <si>
-    <t>2453</t>
-  </si>
-  <si>
-    <t>0.143575</t>
-  </si>
-  <si>
-    <t>0.365188</t>
-  </si>
-  <si>
-    <t>0.267577</t>
-  </si>
-  <si>
-    <t>7.501024</t>
+    <t>2459</t>
+  </si>
+  <si>
+    <t>0.143318</t>
+  </si>
+  <si>
+    <t>0.365588</t>
+  </si>
+  <si>
+    <t>0.267462</t>
+  </si>
+  <si>
+    <t>7.499148</t>
   </si>
   <si>
     <t>署豫：就是后来的山药 《神农本草经》卷一上经的署豫（薯蓣）：味甘温，主伤中、补虚羸、益气力、长肌肉。
@@ -528,19 +648,19 @@
     <t>2026-09-17 08:00:00</t>
   </si>
   <si>
-    <t>2813</t>
-  </si>
-  <si>
-    <t>0.158406</t>
-  </si>
-  <si>
-    <t>0.400803</t>
-  </si>
-  <si>
-    <t>0.234858</t>
-  </si>
-  <si>
-    <t>7.385352</t>
+    <t>2814</t>
+  </si>
+  <si>
+    <t>0.158355</t>
+  </si>
+  <si>
+    <t>0.400989</t>
+  </si>
+  <si>
+    <t>0.234785</t>
+  </si>
+  <si>
+    <t>7.385542</t>
   </si>
   <si>
     <t>木香：辟毒疫温鬼的本经香药 《神农本草经》卷一上经的木香：味辛，主邪气、辟毒疫温鬼、强志。
@@ -552,19 +672,19 @@
     <t>2026-09-16 19:00:00</t>
   </si>
   <si>
-    <t>1310</t>
-  </si>
-  <si>
-    <t>0.119885</t>
-  </si>
-  <si>
-    <t>0.307208</t>
-  </si>
-  <si>
-    <t>0.247726</t>
-  </si>
-  <si>
-    <t>5.695591</t>
+    <t>1317</t>
+  </si>
+  <si>
+    <t>0.120344</t>
+  </si>
+  <si>
+    <t>0.307263</t>
+  </si>
+  <si>
+    <t>0.247905</t>
+  </si>
+  <si>
+    <t>5.699022</t>
   </si>
   <si>
     <t>车前子：牛迹里长出的当道草 《神农本草经》卷一上经的车前子：味甘寒，主气癃、利水道小便、除湿痹。
@@ -576,22 +696,25 @@
     <t>2026-09-16 08:00:00</t>
   </si>
   <si>
-    <t>4856</t>
-  </si>
-  <si>
-    <t>0.210498</t>
-  </si>
-  <si>
-    <t>0.458306</t>
-  </si>
-  <si>
-    <t>0.219980</t>
-  </si>
-  <si>
-    <t>10.194963</t>
+    <t>4862</t>
+  </si>
+  <si>
+    <t>0.210414</t>
+  </si>
+  <si>
+    <t>0.458104</t>
+  </si>
+  <si>
+    <t>0.220057</t>
+  </si>
+  <si>
+    <t>10.188739</t>
   </si>
   <si>
     <t>28</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>独活：无风自动的本经上品 《神农本草经》卷一上经的独活：味苦平，主风寒所击、金疮止痛、女子疝瘕。
@@ -603,22 +726,19 @@
     <t>2026-09-15 20:06:14</t>
   </si>
   <si>
-    <t>2917</t>
-  </si>
-  <si>
-    <t>0.161770</t>
-  </si>
-  <si>
-    <t>0.371988</t>
-  </si>
-  <si>
-    <t>0.274012</t>
-  </si>
-  <si>
-    <t>8.176565</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>2921</t>
+  </si>
+  <si>
+    <t>0.161551</t>
+  </si>
+  <si>
+    <t>0.371713</t>
+  </si>
+  <si>
+    <t>0.274214</t>
+  </si>
+  <si>
+    <t>8.170513</t>
   </si>
   <si>
     <t>麦门冬：别名不死药的润肺上品 《神农本草经》卷一上经的麦门冬：味甘平，主心腹结气、胃络脉绝、羸瘦短气。
@@ -630,19 +750,19 @@
     <t>2026-09-14 08:00:00</t>
   </si>
   <si>
-    <t>961</t>
-  </si>
-  <si>
-    <t>0.159864</t>
-  </si>
-  <si>
-    <t>0.366062</t>
-  </si>
-  <si>
-    <t>0.303095</t>
-  </si>
-  <si>
-    <t>7.515475</t>
+    <t>964</t>
+  </si>
+  <si>
+    <t>0.160633</t>
+  </si>
+  <si>
+    <t>0.367412</t>
+  </si>
+  <si>
+    <t>0.302449</t>
+  </si>
+  <si>
+    <t>7.519702</t>
   </si>
   <si>
     <t>防葵：博物志说它与狼毒相似 《神农本草经》卷一上经的防葵：味辛寒，主疝瘕肠泄、膀胱热结、惊邪狂走。
@@ -654,19 +774,19 @@
     <t>2026-09-13 20:00:00</t>
   </si>
   <si>
-    <t>4268</t>
-  </si>
-  <si>
-    <t>0.159838</t>
-  </si>
-  <si>
-    <t>0.415551</t>
-  </si>
-  <si>
-    <t>0.190065</t>
-  </si>
-  <si>
-    <t>7.665011</t>
+    <t>4278</t>
+  </si>
+  <si>
+    <t>0.159919</t>
+  </si>
+  <si>
+    <t>0.415624</t>
+  </si>
+  <si>
+    <t>0.190117</t>
+  </si>
+  <si>
+    <t>7.664437</t>
   </si>
   <si>
     <t>女萎：就是后来的玉竹 《神农本草经》卷一上经的女萎：味甘平，主中风暴热、跌筋结肉，久服好颜色。
@@ -678,19 +798,19 @@
     <t>2026-09-13 08:00:00</t>
   </si>
   <si>
-    <t>3298</t>
-  </si>
-  <si>
-    <t>0.128972</t>
-  </si>
-  <si>
-    <t>0.401297</t>
-  </si>
-  <si>
-    <t>0.181582</t>
-  </si>
-  <si>
-    <t>7.182879</t>
+    <t>3304</t>
+  </si>
+  <si>
+    <t>0.128834</t>
+  </si>
+  <si>
+    <t>0.401658</t>
+  </si>
+  <si>
+    <t>0.181394</t>
+  </si>
+  <si>
+    <t>7.181653</t>
   </si>
   <si>
     <t>充蔚子：本经里的益母草子 《神农本草经》卷一上经的充蔚子（茺蔚子）：味辛微温，主明目益精、除水气，茎可作浴汤。
@@ -702,19 +822,19 @@
     <t>2026-09-12 19:13:39</t>
   </si>
   <si>
-    <t>758</t>
-  </si>
-  <si>
-    <t>0.147497</t>
-  </si>
-  <si>
-    <t>0.341902</t>
-  </si>
-  <si>
-    <t>0.314910</t>
-  </si>
-  <si>
-    <t>6.976864</t>
+    <t>761</t>
+  </si>
+  <si>
+    <t>0.148448</t>
+  </si>
+  <si>
+    <t>0.342308</t>
+  </si>
+  <si>
+    <t>0.314103</t>
+  </si>
+  <si>
+    <t>6.982051</t>
   </si>
   <si>
     <t>牛膝：陶弘景说它茎像牛膝 《神农本草经》卷一上经的牛膝：味苦酸，主寒湿痿痹、膝痛不可屈伸，逐血气。
@@ -726,19 +846,19 @@
     <t>2026-08-30 14:00:00</t>
   </si>
   <si>
-    <t>3255</t>
-  </si>
-  <si>
-    <t>0.190294</t>
-  </si>
-  <si>
-    <t>0.422197</t>
-  </si>
-  <si>
-    <t>0.236754</t>
-  </si>
-  <si>
-    <t>8.748745</t>
+    <t>3257</t>
+  </si>
+  <si>
+    <t>0.190182</t>
+  </si>
+  <si>
+    <t>0.422520</t>
+  </si>
+  <si>
+    <t>0.236622</t>
+  </si>
+  <si>
+    <t>8.748049</t>
   </si>
   <si>
     <t>菟丝子：本经续绝伤的上品 《神农本草经》卷一上经的菟丝子：味辛平，主续绝伤、益气力、肥健，汁去面皯。
@@ -750,19 +870,19 @@
     <t>2026-08-30 08:00:00</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>0.250000</t>
-  </si>
-  <si>
-    <t>0.423077</t>
-  </si>
-  <si>
-    <t>0.238462</t>
-  </si>
-  <si>
-    <t>7.230769</t>
+    <t>111</t>
+  </si>
+  <si>
+    <t>0.247706</t>
+  </si>
+  <si>
+    <t>0.427481</t>
+  </si>
+  <si>
+    <t>0.236641</t>
+  </si>
+  <si>
+    <t>7.236641</t>
   </si>
   <si>
     <t>术：本经里"长服山精"的上品 《神农本草经》卷一上经的术：味苦温，主风寒湿痹、死肌、痉、疸，止汗除热消食。
@@ -774,19 +894,19 @@
     <t>2026-08-29 14:00:00</t>
   </si>
   <si>
-    <t>2451</t>
-  </si>
-  <si>
-    <t>0.145455</t>
-  </si>
-  <si>
-    <t>0.356399</t>
-  </si>
-  <si>
-    <t>0.254092</t>
-  </si>
-  <si>
-    <t>9.842634</t>
+    <t>2453</t>
+  </si>
+  <si>
+    <t>0.145616</t>
+  </si>
+  <si>
+    <t>0.356241</t>
+  </si>
+  <si>
+    <t>0.254458</t>
+  </si>
+  <si>
+    <t>9.834695</t>
   </si>
   <si>
     <t>干地黄：本经"填骨髓"的第一补药 《神农本草经》卷一上经的干地黄：味甘寒，主折跌绝筋、逐血痹、填骨髓，生者尤良。
@@ -798,19 +918,19 @@
     <t>2026-08-29 08:00:00</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>0.265625</t>
-  </si>
-  <si>
-    <t>0.367089</t>
-  </si>
-  <si>
-    <t>0.316456</t>
-  </si>
-  <si>
-    <t>6.860759</t>
+    <t>73</t>
+  </si>
+  <si>
+    <t>0.276923</t>
+  </si>
+  <si>
+    <t>0.375000</t>
+  </si>
+  <si>
+    <t>0.312500</t>
+  </si>
+  <si>
+    <t>6.925000</t>
   </si>
   <si>
     <t>天门冬：抱朴子也记了它一堆别名 《神农本草经》卷一上经的天门冬：味苦平，主诸暴风湿偏痹，强骨髓，杀三虫。
@@ -822,19 +942,19 @@
     <t>2026-08-28 08:00:00</t>
   </si>
   <si>
-    <t>1858</t>
-  </si>
-  <si>
-    <t>0.143458</t>
-  </si>
-  <si>
-    <t>0.361097</t>
-  </si>
-  <si>
-    <t>0.284408</t>
-  </si>
-  <si>
-    <t>7.360872</t>
+    <t>1865</t>
+  </si>
+  <si>
+    <t>0.143832</t>
+  </si>
+  <si>
+    <t>0.361238</t>
+  </si>
+  <si>
+    <t>0.284627</t>
+  </si>
+  <si>
+    <t>7.365063</t>
   </si>
   <si>
     <t>鞠华：本经里"目欲脱"的菊花 《神农本草经》卷一上经的鞠华（菊花）：味苦平，主风、头眩肿痛、目欲脱、泪出，久服耐老延年。
@@ -846,19 +966,19 @@
     <t>2026-08-27 14:00:00</t>
   </si>
   <si>
-    <t>531</t>
-  </si>
-  <si>
-    <t>0.116487</t>
-  </si>
-  <si>
-    <t>0.300172</t>
-  </si>
-  <si>
-    <t>0.322470</t>
-  </si>
-  <si>
-    <t>5.720412</t>
+    <t>534</t>
+  </si>
+  <si>
+    <t>0.116071</t>
+  </si>
+  <si>
+    <t>0.302048</t>
+  </si>
+  <si>
+    <t>0.322526</t>
+  </si>
+  <si>
+    <t>5.721843</t>
   </si>
   <si>
     <t>菖蒲：通九窍、明耳目的本经上品 《神农本草经》卷一上经的菖蒲：味辛温，主风寒湿痹、咳逆上气，开心孔，通九窍，明耳目。
@@ -870,19 +990,19 @@
     <t>2026-08-27 08:00:00</t>
   </si>
   <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>0.142405</t>
-  </si>
-  <si>
-    <t>0.335244</t>
-  </si>
-  <si>
-    <t>0.355301</t>
-  </si>
-  <si>
-    <t>5.825215</t>
+    <t>320</t>
+  </si>
+  <si>
+    <t>0.141956</t>
+  </si>
+  <si>
+    <t>0.337143</t>
+  </si>
+  <si>
+    <t>0.354286</t>
+  </si>
+  <si>
+    <t>5.837143</t>
   </si>
   <si>
     <t>扁青：本经主折跌痈肿 《神农本草经》里的扁青：味甘平，主目痛、折跌、痈肿、金创不疗，利精神。
@@ -894,16 +1014,19 @@
     <t>2026-08-26 14:00:00</t>
   </si>
   <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>0.129032</t>
-  </si>
-  <si>
-    <t>0.380952</t>
-  </si>
-  <si>
-    <t>7.750000</t>
+    <t>156</t>
+  </si>
+  <si>
+    <t>0.127389</t>
+  </si>
+  <si>
+    <t>0.247059</t>
+  </si>
+  <si>
+    <t>0.382353</t>
+  </si>
+  <si>
+    <t>7.688235</t>
   </si>
   <si>
     <t>白青：可消而为铜的本经石药 《神农本草经》里的白青：味甘平，主明目、利九窍、耳聋，杀诸毒、三虫。
@@ -915,19 +1038,19 @@
     <t>2026-08-26 08:00:00</t>
   </si>
   <si>
-    <t>631</t>
-  </si>
-  <si>
-    <t>0.152695</t>
-  </si>
-  <si>
-    <t>0.350501</t>
-  </si>
-  <si>
-    <t>0.250358</t>
-  </si>
-  <si>
-    <t>11.092990</t>
+    <t>632</t>
+  </si>
+  <si>
+    <t>0.152466</t>
+  </si>
+  <si>
+    <t>0.350000</t>
+  </si>
+  <si>
+    <t>0.251429</t>
+  </si>
+  <si>
+    <t>11.078571</t>
   </si>
   <si>
     <t>紫石英：绝孕十年无子的本经说法 《神农本草经》里的紫石英：味甘温，主心腹咳逆，补不足，有女子风寒在子宫的古说。
@@ -939,19 +1062,19 @@
     <t>2026-08-23 20:35:00</t>
   </si>
   <si>
-    <t>4619</t>
-  </si>
-  <si>
-    <t>0.115978</t>
-  </si>
-  <si>
-    <t>0.355174</t>
-  </si>
-  <si>
-    <t>0.225729</t>
-  </si>
-  <si>
-    <t>7.089093</t>
+    <t>4621</t>
+  </si>
+  <si>
+    <t>0.115930</t>
+  </si>
+  <si>
+    <t>0.355032</t>
+  </si>
+  <si>
+    <t>0.226038</t>
+  </si>
+  <si>
+    <t>7.086861</t>
   </si>
   <si>
     <t>22</t>
@@ -966,19 +1089,19 @@
     <t>2026-08-23 18:32:24</t>
   </si>
   <si>
-    <t>3625</t>
-  </si>
-  <si>
-    <t>0.101251</t>
-  </si>
-  <si>
-    <t>0.332362</t>
-  </si>
-  <si>
-    <t>0.260933</t>
-  </si>
-  <si>
-    <t>5.686589</t>
+    <t>3629</t>
+  </si>
+  <si>
+    <t>0.101398</t>
+  </si>
+  <si>
+    <t>0.331879</t>
+  </si>
+  <si>
+    <t>0.260908</t>
+  </si>
+  <si>
+    <t>5.680628</t>
   </si>
   <si>
     <t>23</t>
@@ -993,19 +1116,19 @@
     <t>2026-08-22 14:50:00</t>
   </si>
   <si>
-    <t>1564</t>
-  </si>
-  <si>
-    <t>0.125837</t>
-  </si>
-  <si>
-    <t>0.397946</t>
-  </si>
-  <si>
-    <t>0.247754</t>
-  </si>
-  <si>
-    <t>7.596277</t>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>0.126000</t>
+  </si>
+  <si>
+    <t>0.397953</t>
+  </si>
+  <si>
+    <t>0.247601</t>
+  </si>
+  <si>
+    <t>7.589891</t>
   </si>
   <si>
     <t>禹余粮：名字从大禹治水来 《神农本草经》里的禹余粮：味甘寒，主咳逆、寒热烦满、血闭症瘕。
@@ -1017,19 +1140,19 @@
     <t>2026-08-22 10:39:43</t>
   </si>
   <si>
-    <t>484</t>
-  </si>
-  <si>
-    <t>0.138568</t>
-  </si>
-  <si>
-    <t>0.327623</t>
-  </si>
-  <si>
-    <t>0.308351</t>
-  </si>
-  <si>
-    <t>5.884368</t>
+    <t>485</t>
+  </si>
+  <si>
+    <t>0.139908</t>
+  </si>
+  <si>
+    <t>0.326964</t>
+  </si>
+  <si>
+    <t>0.307856</t>
+  </si>
+  <si>
+    <t>5.878981</t>
   </si>
   <si>
     <t>曾青：铜之精的本经石药 《神农本草经》里的曾青：味酸小寒，主目痛止泪，破症坚积聚，久服轻身。
@@ -1041,19 +1164,19 @@
     <t>2026-08-21 20:00:00</t>
   </si>
   <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>0.084337</t>
-  </si>
-  <si>
-    <t>0.297619</t>
-  </si>
-  <si>
-    <t>0.404762</t>
-  </si>
-  <si>
-    <t>4.416667</t>
+    <t>84</t>
+  </si>
+  <si>
+    <t>0.083333</t>
+  </si>
+  <si>
+    <t>0.294118</t>
+  </si>
+  <si>
+    <t>0.400000</t>
+  </si>
+  <si>
+    <t>4.388235</t>
   </si>
   <si>
     <t>空青：能化铜铁铅锡作金 《神农本草经》里的空青：味甘寒，主眚盲耳聋，通血脉，养精神，能化铜铁铅锡作金。
@@ -1065,19 +1188,19 @@
     <t>2026-08-21 09:52:17</t>
   </si>
   <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>0.156667</t>
-  </si>
-  <si>
-    <t>0.348243</t>
-  </si>
-  <si>
-    <t>0.287540</t>
-  </si>
-  <si>
-    <t>6.888179</t>
+    <t>290</t>
+  </si>
+  <si>
+    <t>0.155629</t>
+  </si>
+  <si>
+    <t>0.346032</t>
+  </si>
+  <si>
+    <t>0.288889</t>
+  </si>
+  <si>
+    <t>6.857143</t>
   </si>
   <si>
     <t>滑石：利小便的本经石药 《神农本草经》里的滑石：味甘寒，主身热泄、女子乳难、癃闭，利小便，益精气。
@@ -1089,19 +1212,19 @@
     <t>2026-08-19 09:14:26</t>
   </si>
   <si>
-    <t>850</t>
-  </si>
-  <si>
-    <t>0.115385</t>
-  </si>
-  <si>
-    <t>0.281139</t>
-  </si>
-  <si>
-    <t>0.349941</t>
-  </si>
-  <si>
-    <t>5.513642</t>
+    <t>851</t>
+  </si>
+  <si>
+    <t>0.115099</t>
+  </si>
+  <si>
+    <t>0.281657</t>
+  </si>
+  <si>
+    <t>0.349112</t>
+  </si>
+  <si>
+    <t>5.514793</t>
   </si>
   <si>
     <t>24</t>
@@ -1116,19 +1239,19 @@
     <t>2026-08-18 20:00:00</t>
   </si>
   <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>0.114504</t>
-  </si>
-  <si>
-    <t>0.275362</t>
-  </si>
-  <si>
-    <t>0.304348</t>
-  </si>
-  <si>
-    <t>5.217391</t>
+    <t>129</t>
+  </si>
+  <si>
+    <t>0.119403</t>
+  </si>
+  <si>
+    <t>0.276596</t>
+  </si>
+  <si>
+    <t>0.297872</t>
+  </si>
+  <si>
+    <t>5.319149</t>
   </si>
   <si>
     <t>硝石：本经主五脏积热 《神农本草经》里的硝石：味苦寒，主五脏积热，涤去蓄结饮食，推陈致新。
@@ -1140,22 +1263,19 @@
     <t>2026-08-18 09:08:09</t>
   </si>
   <si>
-    <t>3254</t>
-  </si>
-  <si>
-    <t>0.135840</t>
-  </si>
-  <si>
-    <t>0.379654</t>
-  </si>
-  <si>
-    <t>0.235708</t>
-  </si>
-  <si>
-    <t>7.125183</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>3261</t>
+  </si>
+  <si>
+    <t>0.135716</t>
+  </si>
+  <si>
+    <t>0.379320</t>
+  </si>
+  <si>
+    <t>0.236087</t>
+  </si>
+  <si>
+    <t>7.120387</t>
   </si>
   <si>
     <t>涅石：本经里的明矾石 《神农本草经》卷一上经的干地黄：味甘寒，主折跌绝筋、逐血痹、填骨髓，生者尤良。
@@ -1167,19 +1287,19 @@
     <t>2026-08-17 10:01:55</t>
   </si>
   <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>0.161290</t>
-  </si>
-  <si>
-    <t>0.260417</t>
-  </si>
-  <si>
-    <t>0.385417</t>
-  </si>
-  <si>
-    <t>4.802083</t>
+    <t>100</t>
+  </si>
+  <si>
+    <t>0.159574</t>
+  </si>
+  <si>
+    <t>0.257732</t>
+  </si>
+  <si>
+    <t>0.381443</t>
+  </si>
+  <si>
+    <t>4.793814</t>
   </si>
   <si>
     <t>石钟乳：溶洞钟乳也是本草 《神农本草经》里的石钟乳：味甘温，主咳逆上气，通百节，利九窍，下乳汁。
@@ -1191,19 +1311,19 @@
     <t>2026-08-16 08:26:56</t>
   </si>
   <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>0.108137</t>
-  </si>
-  <si>
-    <t>0.287169</t>
-  </si>
-  <si>
-    <t>0.331976</t>
-  </si>
-  <si>
-    <t>5.032587</t>
+    <t>932</t>
+  </si>
+  <si>
+    <t>0.107791</t>
+  </si>
+  <si>
+    <t>0.286294</t>
+  </si>
+  <si>
+    <t>0.330964</t>
+  </si>
+  <si>
+    <t>5.026396</t>
   </si>
   <si>
     <t>玉泉：食玉之说从何而来 《神农本草经》里的玉泉（玉）：味甘平，主柔筋强骨、安魂魄、长肌肉，久服耐寒暑。
@@ -1215,19 +1335,19 @@
     <t>2026-08-15 09:43:06</t>
   </si>
   <si>
-    <t>1258</t>
-  </si>
-  <si>
-    <t>0.105863</t>
-  </si>
-  <si>
-    <t>0.241098</t>
-  </si>
-  <si>
-    <t>0.396142</t>
-  </si>
-  <si>
-    <t>5.241098</t>
+    <t>1261</t>
+  </si>
+  <si>
+    <t>0.105605</t>
+  </si>
+  <si>
+    <t>0.240563</t>
+  </si>
+  <si>
+    <t>0.396743</t>
+  </si>
+  <si>
+    <t>5.233901</t>
   </si>
   <si>
     <t>云母：六个别名的本经上品 《神农本草经》卷一石部之首的云母：味甘平，主身皮死肌、安五脏、益子精、明目。
@@ -1239,19 +1359,19 @@
     <t>2026-08-14 10:38:46</t>
   </si>
   <si>
-    <t>592</t>
-  </si>
-  <si>
-    <t>0.132042</t>
-  </si>
-  <si>
-    <t>0.270400</t>
-  </si>
-  <si>
-    <t>0.360000</t>
-  </si>
-  <si>
-    <t>4.742812</t>
+    <t>594</t>
+  </si>
+  <si>
+    <t>0.131810</t>
+  </si>
+  <si>
+    <t>0.271565</t>
+  </si>
+  <si>
+    <t>0.359425</t>
+  </si>
+  <si>
+    <t>4.748006</t>
   </si>
   <si>
     <t>丹沙：能化为汞的本经石药 《神农本草经》卷一开篇第一味药是丹沙（朱砂）：味甘微寒，养精神，安魂魄，明目。
@@ -1263,19 +1383,19 @@
     <t>2026-08-14 10:24:41</t>
   </si>
   <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>0.117647</t>
-  </si>
-  <si>
-    <t>0.251534</t>
-  </si>
-  <si>
-    <t>0.411043</t>
-  </si>
-  <si>
-    <t>5.196319</t>
+    <t>158</t>
+  </si>
+  <si>
+    <t>0.115385</t>
+  </si>
+  <si>
+    <t>0.253012</t>
+  </si>
+  <si>
+    <t>0.403614</t>
+  </si>
+  <si>
+    <t>5.210843</t>
   </si>
   <si>
     <t>黄耆：痈疽 排脓 小儿百病 《神农本草经》里的黄耆：味甘，微温，主治痈疽久败创、排脓止痛，又补虚、治小儿百病；别名戴糁，生于山谷，二月、十月采。
@@ -1286,19 +1406,19 @@
     <t>2026-08-14 10:18:02</t>
   </si>
   <si>
-    <t>636</t>
-  </si>
-  <si>
-    <t>0.103448</t>
-  </si>
-  <si>
-    <t>0.285489</t>
-  </si>
-  <si>
-    <t>0.359621</t>
-  </si>
-  <si>
-    <t>4.624606</t>
+    <t>640</t>
+  </si>
+  <si>
+    <t>0.104575</t>
+  </si>
+  <si>
+    <t>0.288854</t>
+  </si>
+  <si>
+    <t>0.357928</t>
+  </si>
+  <si>
+    <t>4.653061</t>
   </si>
   <si>
     <t>甘草：古书里写了什么？ 《神农本草经》如何记载甘草？
@@ -1310,19 +1430,19 @@
     <t>2026-08-12 10:38:33</t>
   </si>
   <si>
-    <t>807</t>
-  </si>
-  <si>
-    <t>0.210875</t>
-  </si>
-  <si>
-    <t>0.246675</t>
-  </si>
-  <si>
-    <t>0.379686</t>
-  </si>
-  <si>
-    <t>5.590085</t>
+    <t>812</t>
+  </si>
+  <si>
+    <t>0.213439</t>
+  </si>
+  <si>
+    <t>0.250301</t>
+  </si>
+  <si>
+    <t>0.377858</t>
+  </si>
+  <si>
+    <t>5.599278</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1809,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -1804,195 +1924,195 @@
         <v>28</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>27</v>
@@ -2001,663 +2121,663 @@
         <v>27</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="L7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="P7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="P8" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="O9" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="H12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>39</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="H13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="K15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="P15" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="L16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -2692,272 +2812,272 @@
         <v>171</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="O21" s="1" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="K23" s="1" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="P23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="H24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="K24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="N24" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="L25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="P25" s="1" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -2992,22 +3112,22 @@
         <v>215</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
@@ -3042,7 +3162,7 @@
         <v>222</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>27</v>
@@ -3051,13 +3171,13 @@
         <v>27</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -3092,22 +3212,22 @@
         <v>229</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -3142,22 +3262,22 @@
         <v>236</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -3192,22 +3312,22 @@
         <v>243</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
@@ -3242,22 +3362,22 @@
         <v>250</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -3292,7 +3412,7 @@
         <v>257</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>27</v>
@@ -3301,13 +3421,13 @@
         <v>27</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -3330,19 +3450,19 @@
         <v>261</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>27</v>
@@ -3351,21 +3471,21 @@
         <v>27</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -3374,25 +3494,25 @@
         <v>19</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>27</v>
@@ -3401,10 +3521,10 @@
         <v>27</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>27</v>
@@ -3412,10 +3532,10 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -3424,40 +3544,40 @@
         <v>19</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -3492,157 +3612,157 @@
         <v>285</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="O36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="K37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="O37" s="1" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>27</v>
@@ -3651,49 +3771,49 @@
         <v>27</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L40" s="1" t="s">
         <v>27</v>
       </c>
@@ -3701,13 +3821,13 @@
         <v>27</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -3751,13 +3871,13 @@
         <v>27</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
@@ -3792,22 +3912,22 @@
         <v>329</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -3842,57 +3962,57 @@
         <v>336</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>337</v>
+        <v>37</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="K44" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>27</v>
@@ -3907,93 +4027,93 @@
         <v>27</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="K45" s="1" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="L46" s="1" t="s">
         <v>27</v>
       </c>
@@ -4001,13 +4121,13 @@
         <v>27</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
@@ -4042,7 +4162,7 @@
         <v>365</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>27</v>
@@ -4051,13 +4171,13 @@
         <v>27</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -4092,22 +4212,22 @@
         <v>372</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>39</v>
+        <v>142</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -4142,7 +4262,7 @@
         <v>379</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>27</v>
@@ -4151,13 +4271,13 @@
         <v>27</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
@@ -4192,22 +4312,272 @@
         <v>386</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>39</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/dataExport/作品列表导出.xlsx
+++ b/dataExport/作品列表导出.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
   <si>
     <t>作品名称</t>
   </si>
@@ -64,6 +64,834 @@
   </si>
   <si>
     <t>粉丝增量</t>
+  </si>
+  <si>
+    <t>「腹张」为什么不算错字？ 《神农本草经》百合条：「味甘，平。主邪气腹张，心痛，利大小便，补中益气。」 
+这一集的结论和上一集相反：这个「张」不是抄错的。
+《名医别录》抄的《本经》原文写的也是「张」；到宋代《证类本草》才改成「胀」，
+李时珍也写「胀」，还注明这一句出自《本经》。
+可一千多年后，清代的《醉花窗医案》里还在写「转增腹张」——
+如果这是抄手写错，它不会在一本毫不相干的医案里再出现一次。 
+「张」是旧的写法，「胀」是后来分出来的字。那时候，古人还没把这两个意思分开。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY / CC0）。 
+古籍内容展示，不构成诊疗建议。 
+#神农本草经  #本草纲目  #本草  #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-17 19:00:00</t>
+  </si>
+  <si>
+    <t>1min-视频</t>
+  </si>
+  <si>
+    <t>公开</t>
+  </si>
+  <si>
+    <t>977</t>
+  </si>
+  <si>
+    <t>0.101784</t>
+  </si>
+  <si>
+    <t>0.449102</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.234531</t>
+  </si>
+  <si>
+    <t>12.682635</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>《本经》的「疸痔」，是错字吗？ 《神农本草经》败酱条：「主暴热火创、赤气，疥瘙，疸痔，马鞍热气。」 
+这一集只做一件事：把这一个字的来去查清楚。
+《名医别录》抄的《本经》原文写「疽」，《证类本草》写「疽」，
+李时珍写「疽」，还特意注明这一句出自《本经》——只有底本写「疸」。 
+疸是黄疸，疽是深部的疮。「疥瘙」是皮肤病，和它并列的本该是「疽」。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#神农本草经  #本草纲目  #本草  #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-17 09:06:06</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>0.131245</t>
+  </si>
+  <si>
+    <t>0.503263</t>
+  </si>
+  <si>
+    <t>0.227569</t>
+  </si>
+  <si>
+    <t>16.423328</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>徐长卿：一味药为什么以人名命名？ 《神农本草经》上经里有一味药，名字是一个人的名字：徐长卿。 
+这一集只查一件事——这个名字是从哪来的。
+《本草纲目》释名里，李时珍给的答案很直接：徐长卿，人名也，常以此药治邪病，人遂以名之。 
+而这味药还有另一个名字，是《本经》给的：鬼督邮。督邮，是汉代的一个官。
+两个名字，一个来自一个人，一个来自一个官衔；李时珍还专门把它们拆开——
+「徐长卿之乱鬼督邮，其苗不同，其功同也」。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#神农本草经  #本草纲目  #本草  #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-16 08:00:00</t>
+  </si>
+  <si>
+    <t>6022</t>
+  </si>
+  <si>
+    <t>0.107363</t>
+  </si>
+  <si>
+    <t>0.593826</t>
+  </si>
+  <si>
+    <t>0.166032</t>
+  </si>
+  <si>
+    <t>16.609192</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>白芷：古书里还能做面脂 《神农本草经》卷二·中经载白芷。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主女人漏下赤白，指妇人下血、赤白相杂；血闭，指经血闭止；阴肿，指前阴肿胀；寒热，指寒热往来；风头侵目泪出，指风邪犯头、两目流泪。长肌肤，指使肌肤生长；润泽，指使肌肤润泽；可作面脂，指可以制成涂面的脂膏。一名芳香。生于川谷。
+  注释：「漏下赤白」指妇人下血、赤白相杂；「血闭」指经血闭止；「阴肿」指前阴肿胀；「风头侵目泪出」指风邪犯头、两目流泪。一条经文里，妇人之疾、风邪之疾与「长肌肤，润泽，可作面脂」并列——在本经中，药与面脂本不分家；别名「芳香」，说的正是它的气味。《本草图经》称其「根长尺余，白色」；《本草纲目》记「与白芷同作面脂」，这条汉代的用法一路传了下来。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-15 19:00:00</t>
+  </si>
+  <si>
+    <t>2661</t>
+  </si>
+  <si>
+    <t>0.208531</t>
+  </si>
+  <si>
+    <t>0.446502</t>
+  </si>
+  <si>
+    <t>0.259945</t>
+  </si>
+  <si>
+    <t>7.822016</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>丹参：本经里它叫「却蝉草」 《神农本草经》卷一·上经载丹参。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主心腹邪气，指心腹间的病邪之气；肠鸣幽幽如走水，指肠中鸣响如水流过之声；寒热积聚，指寒热之邪结聚；破症除瘕，指破除腹中结块；止烦满，指止住烦闷胀满；益气，指增益气力。一名却蝉草。生于川谷。
+  注释：「症」与「癥」通假，指腹中结块；「瘕」亦指腹中结块，与「症」相对。一名却蝉草——「却蝉」本作何意，已无其他本子可对证。全库对照：底本作「却蝉草」，后世辑本异文作「蝉蝉草」，两侧均无全库作证。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-15 14:00:00</t>
+  </si>
+  <si>
+    <t>3156</t>
+  </si>
+  <si>
+    <t>0.195235</t>
+  </si>
+  <si>
+    <t>0.401562</t>
+  </si>
+  <si>
+    <t>0.292812</t>
+  </si>
+  <si>
+    <t>8.263438</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>兔缺：吃兔肉会生下唇裂的孩子吗 《饮膳正要》里写着「食兔肉，令子无声缺唇」。
+这句话最早出自《淮南子》，后来五十多部医书写过它。
+唐代有人给过理由，而同一批医书里，外科大夫正在给唇裂的孩子做缝合。
+最后你会发现，答案可能只是一个名字：兔缺。 
+古籍文献展示，不构成医疗建议。 
+#古籍  #传统文化  #冷知识  #历史  #本草</t>
+  </si>
+  <si>
+    <t>2026-10-15 08:00:00</t>
+  </si>
+  <si>
+    <t>1-3min视频</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>0.015306</t>
+  </si>
+  <si>
+    <t>0.239024</t>
+  </si>
+  <si>
+    <t>0.541463</t>
+  </si>
+  <si>
+    <t>7.185366</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>藕实茎：一条药名，为什么把三个部位连在一起？ 《神农本草经》上经里有一条药，名字是三个字：藕实茎。 
+这一集只查一件事——藕、实、茎各指哪个部位。
+答案在这一条的案语里：《说文解字》说，藕，夫渠根；莲，夫渠之实也；茄，夫渠茎。
+三个字，正好是荷的三个部位。 
+可连最早的注家都说不准第三个字。陶弘景注《本草经》时猜：那个「茎」恐怕其实是根。
+到宋代，名字已经串了——蜀地人把藕叫茄，而「茄」本是茎的名字。
+到明代，李时珍做释名，发现连「荷」这个字指哪个部位都不统一。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#神农本草经  #说文解字  #本草纲目   #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-14 19:00:00</t>
+  </si>
+  <si>
+    <t>2185</t>
+  </si>
+  <si>
+    <t>0.124693</t>
+  </si>
+  <si>
+    <t>0.574905</t>
+  </si>
+  <si>
+    <t>0.161260</t>
+  </si>
+  <si>
+    <t>17.243798</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>百合：古书写「腹张」不是错字 《神农本草经》卷二·中经载百合。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主邪气腹张，「腹张」即腹胀，指腹部胀满；心痛，指心下痛；利大小便，指通利大小便；补中益气，指补益中焦、增益气力。生于川谷。
+  注释：「腹张」是「腹胀」的汉代写法，「张」与「胀」通假——全库《神农本草经》本条作「腹张」，《证类本草》等后世辑本多作「腹胀」，意思一致。一条 28 字的经文，没有别名（「一名…」），也没有生境之外的细节，写得相当克制。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-13 14:00:00</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>0.187016</t>
+  </si>
+  <si>
+    <t>0.372814</t>
+  </si>
+  <si>
+    <t>0.300620</t>
+  </si>
+  <si>
+    <t>7.772138</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>「沥节痛」是什么痛？《神农本草经》里的一个错字 《神农本草经》天雄条：「主大风，寒湿痹，沥节痛，拘挛缓急……」 
+这一集只做一件事：把这一个字的来去查清楚。
+宋代的《证类本草》写「历节痛」，明代的《本草纲目》也写「历节痛」，
+并注明这一句出自《本经》；而「历节」是张仲景在《金匮要略》里立下的病名。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#神农本草经  #本草纲目  #本草  #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-13 08:00:00</t>
+  </si>
+  <si>
+    <t>3408</t>
+  </si>
+  <si>
+    <t>0.106088</t>
+  </si>
+  <si>
+    <t>0.421830</t>
+  </si>
+  <si>
+    <t>0.268674</t>
+  </si>
+  <si>
+    <t>11.420382</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>葛根：它的别名比药名还怪 《神农本草经》卷二·中经载葛根。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主消渴，指汉代所称的多饮多尿、消瘦之病；身大热，指身体大热；呕吐，指呕吐；诸痹，指各种痹症；起阴气，指升提阴气；解诸毒，指解各种毒。葛谷，指葛的种子，主下利十岁以上，指十年以上的下利。一名鸡齐根。生于川谷。
+  注释：「消渴」是汉代病名，指多饮多尿、消瘦的病证。「诸痹」泛指各种痹症，「起阴气」指升提阴气，「下利」指泄泻。「葛谷」是葛的种子，与葛根同条而所主不同——「主下利十岁以上」是葛谷条下的那句话，不是葛根的。底本此条作「生种谷」，《本草经集注》《新修本草》《证类本草》并作「生汶山川谷」，「种」当为「川」之形讹，今从他本。一名鸡齐根。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-12 19:00:00</t>
+  </si>
+  <si>
+    <t>5625</t>
+  </si>
+  <si>
+    <t>0.254757</t>
+  </si>
+  <si>
+    <t>0.475426</t>
+  </si>
+  <si>
+    <t>0.198844</t>
+  </si>
+  <si>
+    <t>9.722936</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>防己：一味药为什么以「险健之人」为名？ 《本草纲目》引李杲的话：「防己如险健之人，幸灾乐祸，能首为乱阶，若善用之，亦可御敌。」 
+这一集只做一件事：查「防己」与「解离」这两个名字的来处。
+《本经》给它的别名是「解离」，李时珍说那是因为根上的黑纹散解；
+陶弘景写它「内有黑纹如车辐解者，良」。 
+照录原文，未改一字。实物照来自 iNaturalist（CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#本草纲目  #神农本草经  #本草  #古籍  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-12 08:00:00</t>
+  </si>
+  <si>
+    <t>4951</t>
+  </si>
+  <si>
+    <t>0.084313</t>
+  </si>
+  <si>
+    <t>0.459204</t>
+  </si>
+  <si>
+    <t>0.231141</t>
+  </si>
+  <si>
+    <t>12.165384</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>王不留行：一味药的名字，为什么像一句军令？ 《本草纲目》【释名】：「此物性走而不住，虽有王命不能留其行，故名。」 
+这一集只做一件事：查清这四个字是怎么来的。
+它还有禁宫花、剪金花、金盏银台三个别名，都取自它的花；
+《吴普本草》把它写成「王不流行」，李时珍说那是错的。 
+照录原文，未改一字。实物照来自 iNaturalist（CC0 / CC BY）。 
+古籍内容展示，不构成诊疗建议。 
+#本草纲目  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-10 14:00:00</t>
+  </si>
+  <si>
+    <t>7688</t>
+  </si>
+  <si>
+    <t>0.156564</t>
+  </si>
+  <si>
+    <t>0.496878</t>
+  </si>
+  <si>
+    <t>0.222262</t>
+  </si>
+  <si>
+    <t>14.545989</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>营实：它就是蔷薇的果实 《神农本草经》卷一·上经载营实。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主痈疽恶创，指痈疽与凶恶的创伤；结肉跌筋，指使断裂的肉与筋重新结连；败创，指溃烂的创面；热气，指热邪之病；阴蚀不疗，指下部阴处的侵蚀未能治好；利关节，指使关节通利。
+  注释：「痈疽」指脓肿，「跌筋」指筋之受伤，「阴蚀」指外阴部的侵蚀。三个别名「墙薇、墙麻、牛棘」里「墙薇」就是蔷薇——本草别名常见「墙」「蔷」互通。陶弘景直说：「营实即蔷薇子也，以白花者为良」——它就是蔷薇的果实（rose hip），白花的入药更佳。李时珍另记蔷薇的嫩芽可食：「春抽嫩蕻，小儿掐去皮刺食之」——小孩剥了刺吃它的嫩芽。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-10 08:00:00</t>
+  </si>
+  <si>
+    <t>1395</t>
+  </si>
+  <si>
+    <t>0.190761</t>
+  </si>
+  <si>
+    <t>0.400000</t>
+  </si>
+  <si>
+    <t>0.279032</t>
+  </si>
+  <si>
+    <t>7.438710</t>
+  </si>
+  <si>
+    <t>《神农本草经》为什么把橘和柚写成一味药？ 《神农本草经》「橘柚」条的末尾写着：「一名橘皮。」 
+这一集只做一件事：把这一对药名的来历追清楚。
+宋代的寇宗奭说，橘和柚本来就是两种，《本草》只写了「一名橘皮」，
+是后人误加了「柚」字；到明代，李时珍把柚单独立了一条。 
+照录原文，未改一字。实物照来自 iNaturalist（CC0 / CC BY）。 
+古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-09 14:00:00</t>
+  </si>
+  <si>
+    <t>1958</t>
+  </si>
+  <si>
+    <t>0.113503</t>
+  </si>
+  <si>
+    <t>0.479694</t>
+  </si>
+  <si>
+    <t>0.257525</t>
+  </si>
+  <si>
+    <t>13.336837</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>漏芦：它和神话里的风神同名 《神农本草经》卷一·上经载漏芦。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主皮肤热，指皮肤发热；恶创，指凶恶的创伤；疽痔，指痈疽与痔疮；湿痹，指湿邪所致的痹症；下乳汁，指通下乳汁。久食，指长期服食，身体轻健、增益气力，耳聪目明，不显衰老、延长寿命。
+  注释：「恶创」指凶恶的创伤，「疽痔」指痈疽与痔疮，「湿痹」是汉代对湿邪致痹的称法。这一条的名字有两层：《广雅》直说「飞廉，漏芦也」——「飞廉」又是神话里管风的神（亦写作「蜚廉」），所以名字撞了风神。陶弘景另记民间的叫法：「俗中取根，名鹿骊」——百姓挖根用，叫它「鹿骊」。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-09 08:00:00</t>
+  </si>
+  <si>
+    <t>723</t>
+  </si>
+  <si>
+    <t>0.101064</t>
+  </si>
+  <si>
+    <t>0.267097</t>
+  </si>
+  <si>
+    <t>0.379355</t>
+  </si>
+  <si>
+    <t>7.205161</t>
+  </si>
+  <si>
+    <t>古书里，大枣的叶子为什么单占一行？ 《神农本草经》卷一·上经「大枣」条的最后一句：「叶覆麻黄，能令出汗。」 
+这一集只做一件事：把这一句从唐代追到明代。
+《千金翼方》在果部给枣叶单立了一篇，篇名就叫「叶」；《证类本草》照收；
+《本草纲目》注明它出自《本经》；《本草乘雅半偈》给了它一个解释。 
+照录原文，未改一字。实物照来自 iNaturalist（CC0 / CC BY）。 
+古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-08 21:44:32</t>
+  </si>
+  <si>
+    <t>1874</t>
+  </si>
+  <si>
+    <t>0.087971</t>
+  </si>
+  <si>
+    <t>0.404507</t>
+  </si>
+  <si>
+    <t>0.308169</t>
+  </si>
+  <si>
+    <t>10.762817</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>续断：两个名字都按用处起 《神农本草经》卷一·上经载续断。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主伤寒，指外感伤寒一类的病；补不足，指补益虚损；金创痈伤，指金属器物所伤与疮痈；折跌，指跌打损伤；续筋骨，指接续筋骨；妇人乳难，指妇人乳汁不下或难产的古说。久食，指长期服食，增益气力。
+  注释：「金创」指金属器物所伤，「折跌」指跌打损伤。名字是按用处起的：《本草纲目》说「续断、属折、接骨，皆以功命名也」——底本的两个名字「续断」与「属折」、以及后世《别录》的「接骨」，说的是同一件事。产地底本只作「生山」，《别录》作「生常山山谷」，七月、八月采，阴干。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-07 19:00:00</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>0.184654</t>
+  </si>
+  <si>
+    <t>0.366935</t>
+  </si>
+  <si>
+    <t>0.293548</t>
+  </si>
+  <si>
+    <t>7.845535</t>
+  </si>
+  <si>
+    <t>香蒲：嫩叶是《周礼》里的一道菜 《神农本草经》卷一·上经载香蒲。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主五脏心下邪气，指五脏与心下的邪气；口中烂臭，指口中溃烂臭秽；坚齿，指使牙齿坚固；明目、聪耳，指使目力清明、听觉灵敏。久食，指长期服食，身体轻健、不显衰老。
+  注释：「口中烂臭」指口中溃烂臭秽，「聪耳」指听觉灵敏。这一条与上一条蒲黄是同一株植物：《本草图经》说「香蒲，蒲黄苗也」——蒲黄是它穗上的花粉，它是蒲黄的植株。图经又说「春初生嫩叶，未出水时，红白色，茸茸然，《周礼》以为菹」：嫩叶在未出水时采下，是《周礼》里的一种腌菜。《吴普》记「睢，一名睢石，一名香蒲」，《名医》记「一名醮，生南海」。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-07 08:00:00</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>0.124067</t>
+  </si>
+  <si>
+    <t>0.279894</t>
+  </si>
+  <si>
+    <t>0.362267</t>
+  </si>
+  <si>
+    <t>5.886625</t>
+  </si>
+  <si>
+    <t>蒲黄：香蒲穗子上的黄粉 《神农本草经》卷一·上经载蒲黄。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主心腹、膀胱寒热，指胸腹与膀胱的寒热之病；利小便，指使小便通利；止血，指止住出血；消瘀血，指消散瘀血。久食，指长期服食，身体轻健、气力增益，延长寿命。
+  注释：「心腹」指胸腹，「膀胱寒热」是汉代对下焦寒热病证的称法。这一条的药是花粉，不是草叶：底本案语引《玉篇》说「蒲头有台，台上有重台，中出黄，即蒲黄」，陶弘景说得更直白——「此即蒲厘花上黄粉也」。《名医》记「生河东，四月采」，即农历四月采收。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-06 20:00:00</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>0.130996</t>
+  </si>
+  <si>
+    <t>0.289497</t>
+  </si>
+  <si>
+    <t>0.316858</t>
+  </si>
+  <si>
+    <t>5.736981</t>
+  </si>
+  <si>
+    <t>肉松蓉：名字的意思是「从容」 《神农本草经》卷一·上经载肉松蓉。
+  本片照录原文，并配实物照片；今译与注释见下。
+  今译：古籍称其主五劳七伤，指虚劳诸损的古说；补中，指补益中焦；除茎中寒热痛，指解除前阴部的寒热疼痛；养五脏，指滋养五脏；强阴，指使阴分强健；益精气，指增益精气；多子，指使人多子；妇人症瘕，指妇人腹内的结块。久食，指长期服食，身体轻健。
+  注释：「五劳七伤」是汉代对虚损的概括，「茎」指前阴，「症瘕」指腹内结块。底本作「肉松蓉」：《吴普》说「一名肉松蓉」，孙星衍案「蓉，即是容字，俗写苁蓉，非正字也」——今天通行的「肉苁蓉」是俗写。《本草纲目》说「此物补而不峻，故有从容之号。从容，和缓之貌」，名字说的是药性不急。陶弘景另记一种旧说，说它是「野马精落地所生，生时似肉」，孙星衍已辨其非。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-06 08:00:00</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>0.174950</t>
+  </si>
+  <si>
+    <t>0.364651</t>
+  </si>
+  <si>
+    <t>0.273488</t>
+  </si>
+  <si>
+    <t>7.007442</t>
+  </si>
+  <si>
+    <t>蒺藜子：别名「屈人」，因为扎人 《神农本草经》卷一·上经载蒺藜子。
+  本片照录原文，并配果实照片；今译与注释见下。
+  今译：古籍称其主恶血，指瘀血；破症结积聚，指消散腹内的结块积聚；喉痹，指咽喉肿痛一类的病；乳难，指乳汁不下或难产的古说。久食，指长期服食，能增长肌肉，目力清明、身体轻健。
+  注释：「症结积聚」是汉代对腹内结块的称法，「喉痹」「乳难」也都是汉代病名。「旁通」「屈人」「止行」「豺羽」「升推」是这一条的五个别名：《本草纲目》说「屈人、止行，皆因其伤人也」——果实有刺，碍人行走。《本草经赞》引陶弘景说它「多生道旁及墙头，其叶布地，子有刺状如菱」。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-05 20:07:09</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>0.173367</t>
+  </si>
+  <si>
+    <t>0.367178</t>
+  </si>
+  <si>
+    <t>0.310508</t>
+  </si>
+  <si>
+    <t>14.087367</t>
+  </si>
+  <si>
+    <t>龙眼：也叫益智 《神农本草经》卷二·中经载龙眼。
+  本片照录原文，逐句今译，并说明「安志厌食」的「厌」在汉代读平声、义为饱足。
+  配图为结果的龙眼树。
+  古籍内容展示，不构成诊疗建议。
+ #神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-04 19:00:00</t>
+  </si>
+  <si>
+    <t>1775</t>
+  </si>
+  <si>
+    <t>0.053143</t>
+  </si>
+  <si>
+    <t>0.284171</t>
+  </si>
+  <si>
+    <t>0.311183</t>
+  </si>
+  <si>
+    <t>6.412750</t>
+  </si>
+  <si>
+    <t>藕实茎：藕、莲、茄的分辨 《神农本草经》卷一·上经载藕实茎。
+  本片照录原文，逐句今译，并说明藕、莲、茄是同一株植物的根、实、茎。
+  配图为荷花。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-04 08:00:00</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>0.109057</t>
+  </si>
+  <si>
+    <t>0.353659</t>
+  </si>
+  <si>
+    <t>0.275261</t>
+  </si>
+  <si>
+    <t>8.076655</t>
+  </si>
+  <si>
+    <t>胡麻：古书里的巨胜 《神农本草经》卷一·上经载胡麻。
+  本片照录原文，逐句今译，并说明其古名「巨胜」，以及叶名「青襄」的来历。
+  配图为芝麻。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-03 19:00:00</t>
+  </si>
+  <si>
+    <t>2458</t>
+  </si>
+  <si>
+    <t>0.075949</t>
+  </si>
+  <si>
+    <t>0.362966</t>
+  </si>
+  <si>
+    <t>0.223991</t>
+  </si>
+  <si>
+    <t>8.791149</t>
+  </si>
+  <si>
+    <t>葡萄：可作酒的那一味 《神农本草经》卷一·上经载葡萄。
+  本片照录原文，逐句今译，并说明汉代病名「湿痹」；经文末句「可作酒」是葡萄入汉的早期线索。
+  配图为结实的葡萄。
+  古籍内容展示，不构成诊疗建议。
+ #神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-03 08:00:00</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>0.054460</t>
+  </si>
+  <si>
+    <t>0.258711</t>
+  </si>
+  <si>
+    <t>0.337979</t>
+  </si>
+  <si>
+    <t>6.545296</t>
+  </si>
+  <si>
+    <t>橘柚：入药取的是皮 《神农本草经》卷一·上经载橘柚。
+  本片照录原文，逐句今译，并说明汉代病名「瘕」，以及「通神」一词的方术语义。
+  配图为柚树。
+  古籍内容展示，不构成诊疗建议。
+ #神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-02 19:00:00</t>
+  </si>
+  <si>
+    <t>1296</t>
+  </si>
+  <si>
+    <t>0.063396</t>
+  </si>
+  <si>
+    <t>0.325564</t>
+  </si>
+  <si>
+    <t>0.327749</t>
+  </si>
+  <si>
+    <t>5.998543</t>
+  </si>
+  <si>
+    <t>大枣：一味和百药的本草 《神农本草经》卷一·上经载大枣。
+  本片照录原文，逐句今译；底本「肋十二经」据《证类本草》校作「助十二经」，末句讲的是枣叶而非枣实。
+  配图为结果期的枣树。
+  古籍内容展示，不构成诊疗建议。
+#神农本草经  #本草  #古籍  #传统文化  #读书</t>
+  </si>
+  <si>
+    <t>2026-10-02 13:47:48</t>
+  </si>
+  <si>
+    <t>1859</t>
+  </si>
+  <si>
+    <t>0.037693</t>
+  </si>
+  <si>
+    <t>0.251237</t>
+  </si>
+  <si>
+    <t>0.363386</t>
+  </si>
+  <si>
+    <t>5.682793</t>
   </si>
   <si>
     <t>决明子：又名草决明 《神农本草经》卷一·上经载决明子。
@@ -75,40 +903,19 @@
     <t>2026-10-01 19:00:00</t>
   </si>
   <si>
-    <t>1min-视频</t>
-  </si>
-  <si>
-    <t>公开</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>0.112142</t>
-  </si>
-  <si>
-    <t>0.399072</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.235112</t>
-  </si>
-  <si>
-    <t>10.778036</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1224</t>
+  </si>
+  <si>
+    <t>0.108679</t>
+  </si>
+  <si>
+    <t>0.389564</t>
+  </si>
+  <si>
+    <t>0.242316</t>
+  </si>
+  <si>
+    <t>10.346676</t>
   </si>
   <si>
     <t>防风：古书说的「大风」是什么 《神农本草经》卷一·上经载防风。
@@ -120,28 +927,19 @@
     <t>2026-10-01 08:00:00</t>
   </si>
   <si>
-    <t>689</t>
-  </si>
-  <si>
-    <t>0.044140</t>
-  </si>
-  <si>
-    <t>0.241679</t>
-  </si>
-  <si>
-    <t>0.429812</t>
-  </si>
-  <si>
-    <t>5.342981</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>791</t>
+  </si>
+  <si>
+    <t>0.048322</t>
+  </si>
+  <si>
+    <t>0.250951</t>
+  </si>
+  <si>
+    <t>0.422053</t>
+  </si>
+  <si>
+    <t>5.361217</t>
   </si>
   <si>
     <t>蓝实：古书里的染青草 《神农本草经》卷一·上经载蓝实。
@@ -153,25 +951,19 @@
     <t>2026-09-30 19:00:00</t>
   </si>
   <si>
-    <t>708</t>
-  </si>
-  <si>
-    <t>0.092414</t>
-  </si>
-  <si>
-    <t>0.283444</t>
-  </si>
-  <si>
-    <t>0.324503</t>
-  </si>
-  <si>
-    <t>6.480795</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>739</t>
+  </si>
+  <si>
+    <t>0.091270</t>
+  </si>
+  <si>
+    <t>0.279898</t>
+  </si>
+  <si>
+    <t>0.326972</t>
+  </si>
+  <si>
+    <t>6.408397</t>
   </si>
   <si>
     <t>紫芝：六芝之一，色紫如桑 《神农本草经》卷一·上经载紫芝。
@@ -183,19 +975,19 @@
     <t>2026-09-30 08:00:00</t>
   </si>
   <si>
-    <t>1863</t>
-  </si>
-  <si>
-    <t>0.062771</t>
-  </si>
-  <si>
-    <t>0.343880</t>
-  </si>
-  <si>
-    <t>0.241183</t>
-  </si>
-  <si>
-    <t>7.210062</t>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>0.062434</t>
+  </si>
+  <si>
+    <t>0.344162</t>
+  </si>
+  <si>
+    <t>0.242640</t>
+  </si>
+  <si>
+    <t>7.178680</t>
   </si>
   <si>
     <t>黄芝：古书说它黄如紫金 《神农本草经》卷一·上经载黄芝。
@@ -207,19 +999,19 @@
     <t>2026-09-27 19:19:09</t>
   </si>
   <si>
-    <t>1667</t>
-  </si>
-  <si>
-    <t>0.067463</t>
-  </si>
-  <si>
-    <t>0.323569</t>
-  </si>
-  <si>
-    <t>0.209128</t>
-  </si>
-  <si>
-    <t>6.051090</t>
+    <t>1693</t>
+  </si>
+  <si>
+    <t>0.069751</t>
+  </si>
+  <si>
+    <t>0.324415</t>
+  </si>
+  <si>
+    <t>0.210702</t>
+  </si>
+  <si>
+    <t>6.073579</t>
   </si>
   <si>
     <t>白芝：入肺应秋的玉芝 《神农本草经》卷一上经的白芝：味辛平，主咳逆上气、益肺气、通利口鼻、安魄。
@@ -231,28 +1023,19 @@
     <t>2026-09-25 08:00:00</t>
   </si>
   <si>
-    <t>1961</t>
-  </si>
-  <si>
-    <t>0.140010</t>
-  </si>
-  <si>
-    <t>0.343812</t>
-  </si>
-  <si>
-    <t>0.273453</t>
-  </si>
-  <si>
-    <t>6.667665</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>0.141378</t>
+  </si>
+  <si>
+    <t>0.346969</t>
+  </si>
+  <si>
+    <t>0.271562</t>
+  </si>
+  <si>
+    <t>6.692952</t>
   </si>
   <si>
     <t>青芝：入肝应春的明目芝 《神农本草经》卷一上经的青芝：味酸平，主明目、补肝气、安精魂。
@@ -264,22 +1047,19 @@
     <t>2026-09-24 19:00:00</t>
   </si>
   <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>0.125693</t>
-  </si>
-  <si>
-    <t>0.294271</t>
-  </si>
-  <si>
-    <t>0.317708</t>
-  </si>
-  <si>
-    <t>6.446181</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>0.130204</t>
+  </si>
+  <si>
+    <t>0.297521</t>
+  </si>
+  <si>
+    <t>0.319835</t>
+  </si>
+  <si>
+    <t>6.581818</t>
   </si>
   <si>
     <t>赤芝：六芝之首的安神上品 《神农本草经》卷一上经的赤芝：味苦平，益心气、补中、增智慧、不忘。
@@ -291,25 +1071,19 @@
     <t>2026-09-24 08:00:00</t>
   </si>
   <si>
-    <t>2961</t>
-  </si>
-  <si>
-    <t>0.113001</t>
-  </si>
-  <si>
-    <t>0.309293</t>
-  </si>
-  <si>
-    <t>0.283788</t>
-  </si>
-  <si>
-    <t>5.912049</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>2998</t>
+  </si>
+  <si>
+    <t>0.114286</t>
+  </si>
+  <si>
+    <t>0.310185</t>
+  </si>
+  <si>
+    <t>0.282697</t>
+  </si>
+  <si>
+    <t>5.905961</t>
   </si>
   <si>
     <t>蓍实：占筮用的百茎之草 《神农本草经》卷一上经的蓍实：味苦平，主益气充肌肤，明目聪慧先知。
@@ -321,22 +1095,19 @@
     <t>2026-09-23 20:00:00</t>
   </si>
   <si>
-    <t>1081</t>
-  </si>
-  <si>
-    <t>0.188215</t>
-  </si>
-  <si>
-    <t>0.422824</t>
-  </si>
-  <si>
-    <t>0.226601</t>
-  </si>
-  <si>
-    <t>6.987685</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>0.188793</t>
+  </si>
+  <si>
+    <t>0.422705</t>
+  </si>
+  <si>
+    <t>0.229469</t>
+  </si>
+  <si>
+    <t>6.965378</t>
   </si>
   <si>
     <t>奄闾子：食之神仙的蒿类 《神农本草经》卷一上经的奄闾子：味苦微寒，主五脏瘀血、腹中水气、身体诸痛。
@@ -348,19 +1119,19 @@
     <t>2026-09-23 08:00:00</t>
   </si>
   <si>
-    <t>793</t>
-  </si>
-  <si>
-    <t>0.174037</t>
-  </si>
-  <si>
-    <t>0.433962</t>
-  </si>
-  <si>
-    <t>0.253369</t>
-  </si>
-  <si>
-    <t>8.045760</t>
+    <t>819</t>
+  </si>
+  <si>
+    <t>0.176634</t>
+  </si>
+  <si>
+    <t>0.432503</t>
+  </si>
+  <si>
+    <t>0.252949</t>
+  </si>
+  <si>
+    <t>7.996073</t>
   </si>
   <si>
     <t>析子：俗呼老荠的明目药 《神农本草经》卷一上经的析子（菥蓂）：味辛微温，主目痛泪出、益精光。
@@ -372,19 +1143,19 @@
     <t>2026-09-22 20:00:00</t>
   </si>
   <si>
-    <t>667</t>
-  </si>
-  <si>
-    <t>0.147994</t>
-  </si>
-  <si>
-    <t>0.370904</t>
-  </si>
-  <si>
-    <t>0.251638</t>
-  </si>
-  <si>
-    <t>8.705111</t>
+    <t>682</t>
+  </si>
+  <si>
+    <t>0.148299</t>
+  </si>
+  <si>
+    <t>0.369369</t>
+  </si>
+  <si>
+    <t>0.249678</t>
+  </si>
+  <si>
+    <t>8.635779</t>
   </si>
   <si>
     <t>赤箭：其实就是天麻 《神农本草经》卷一上经的赤箭：味辛温，主杀鬼精物蛊毒恶气，久服增年。
@@ -396,19 +1167,19 @@
     <t>2026-09-22 08:00:00</t>
   </si>
   <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>0.151572</t>
-  </si>
-  <si>
-    <t>0.376118</t>
-  </si>
-  <si>
-    <t>0.220930</t>
-  </si>
-  <si>
-    <t>8.146691</t>
+    <t>1918</t>
+  </si>
+  <si>
+    <t>0.153667</t>
+  </si>
+  <si>
+    <t>0.376779</t>
+  </si>
+  <si>
+    <t>0.220196</t>
+  </si>
+  <si>
+    <t>8.169039</t>
   </si>
   <si>
     <t>白蒿：《诗经》里的采蘩 《神农本草经》卷一上经的白蒿：味甘平，补中益气，长毛发令黑，疗心悬。
@@ -420,22 +1191,19 @@
     <t>2026-09-21 19:00:00</t>
   </si>
   <si>
-    <t>1968</t>
-  </si>
-  <si>
-    <t>0.120821</t>
-  </si>
-  <si>
-    <t>0.331050</t>
-  </si>
-  <si>
-    <t>0.256164</t>
-  </si>
-  <si>
-    <t>5.887215</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>0.121847</t>
+  </si>
+  <si>
+    <t>0.332271</t>
+  </si>
+  <si>
+    <t>0.255803</t>
+  </si>
+  <si>
+    <t>5.895312</t>
   </si>
   <si>
     <t>白英：江东呼为鬼目草 《神农本草经》卷一上经的白英：味甘寒，主寒热八疽消渴，补中益气。
@@ -447,22 +1215,19 @@
     <t>2026-09-21 08:00:00</t>
   </si>
   <si>
-    <t>2948</t>
-  </si>
-  <si>
-    <t>0.164314</t>
-  </si>
-  <si>
-    <t>0.384197</t>
-  </si>
-  <si>
-    <t>0.240767</t>
-  </si>
-  <si>
-    <t>8.964787</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>2972</t>
+  </si>
+  <si>
+    <t>0.164776</t>
+  </si>
+  <si>
+    <t>0.384353</t>
+  </si>
+  <si>
+    <t>0.240967</t>
+  </si>
+  <si>
+    <t>8.952489</t>
   </si>
   <si>
     <t>巴戟天：强筋骨、增志的上品 《神农本草经》卷一上经的巴戟天：味辛微温，主大风邪气、阴痿不起、增志。
@@ -474,19 +1239,19 @@
     <t>2026-09-20 19:00:00</t>
   </si>
   <si>
-    <t>3018</t>
-  </si>
-  <si>
-    <t>0.188077</t>
-  </si>
-  <si>
-    <t>0.426425</t>
-  </si>
-  <si>
-    <t>0.222943</t>
-  </si>
-  <si>
-    <t>7.624445</t>
+    <t>3036</t>
+  </si>
+  <si>
+    <t>0.188846</t>
+  </si>
+  <si>
+    <t>0.426635</t>
+  </si>
+  <si>
+    <t>0.223314</t>
+  </si>
+  <si>
+    <t>7.609285</t>
   </si>
   <si>
     <t>20</t>
@@ -501,19 +1266,19 @@
     <t>2026-09-20 14:08:36</t>
   </si>
   <si>
-    <t>585</t>
-  </si>
-  <si>
-    <t>0.152000</t>
-  </si>
-  <si>
-    <t>0.381024</t>
-  </si>
-  <si>
-    <t>0.251506</t>
-  </si>
-  <si>
-    <t>7.335843</t>
+    <t>596</t>
+  </si>
+  <si>
+    <t>0.155660</t>
+  </si>
+  <si>
+    <t>0.384615</t>
+  </si>
+  <si>
+    <t>0.251479</t>
+  </si>
+  <si>
+    <t>7.335799</t>
   </si>
   <si>
     <t>细辛：华阴色白者为善 《神农本草经》卷一上经的细辛：味辛温，主头痛脑动、百节拘挛、风湿痹痛。
@@ -525,19 +1290,19 @@
     <t>2026-09-19 19:00:00</t>
   </si>
   <si>
-    <t>1376</t>
-  </si>
-  <si>
-    <t>0.109453</t>
-  </si>
-  <si>
-    <t>0.299523</t>
-  </si>
-  <si>
-    <t>0.353302</t>
-  </si>
-  <si>
-    <t>5.703880</t>
+    <t>1394</t>
+  </si>
+  <si>
+    <t>0.111111</t>
+  </si>
+  <si>
+    <t>0.300808</t>
+  </si>
+  <si>
+    <t>0.351952</t>
+  </si>
+  <si>
+    <t>5.722073</t>
   </si>
   <si>
     <t>龙胆：主骨间寒热的苦口上品 《神农本草经》卷一上经的龙胆：味苦涩，主惊痫邪气、续绝伤、杀蛊毒。
@@ -549,22 +1314,19 @@
     <t>2026-09-19 08:00:00</t>
   </si>
   <si>
-    <t>2977</t>
-  </si>
-  <si>
-    <t>0.149070</t>
-  </si>
-  <si>
-    <t>0.364557</t>
-  </si>
-  <si>
-    <t>0.269620</t>
-  </si>
-  <si>
-    <t>7.194304</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>2995</t>
+  </si>
+  <si>
+    <t>0.148796</t>
+  </si>
+  <si>
+    <t>0.362893</t>
+  </si>
+  <si>
+    <t>0.269497</t>
+  </si>
+  <si>
+    <t>7.171069</t>
   </si>
   <si>
     <t>远志：它的叶子叫小草 《神农本草经》卷一上经的远志：味苦温，利九窍、益智慧、不忘、强志倍力。
@@ -576,19 +1338,16 @@
     <t>2026-09-18 19:00:00</t>
   </si>
   <si>
-    <t>1959</t>
-  </si>
-  <si>
-    <t>0.127797</t>
-  </si>
-  <si>
-    <t>0.306818</t>
-  </si>
-  <si>
-    <t>0.329072</t>
-  </si>
-  <si>
-    <t>6.126894</t>
+    <t>0.127566</t>
+  </si>
+  <si>
+    <t>0.307728</t>
+  </si>
+  <si>
+    <t>0.329609</t>
+  </si>
+  <si>
+    <t>6.130354</t>
   </si>
   <si>
     <t>泽泻：能行水上的本经奇谈 《神农本草经》卷一上经的泽泻：味甘寒，主风寒湿痹、乳难，消水养五脏。
@@ -600,19 +1359,19 @@
     <t>2026-09-18 08:00:00</t>
   </si>
   <si>
-    <t>2800</t>
-  </si>
-  <si>
-    <t>0.145910</t>
-  </si>
-  <si>
-    <t>0.364275</t>
-  </si>
-  <si>
-    <t>0.238360</t>
-  </si>
-  <si>
-    <t>7.504246</t>
+    <t>2821</t>
+  </si>
+  <si>
+    <t>0.146460</t>
+  </si>
+  <si>
+    <t>0.365569</t>
+  </si>
+  <si>
+    <t>0.237693</t>
+  </si>
+  <si>
+    <t>7.510923</t>
   </si>
   <si>
     <t>薏苡仁：马援常饵的轻身药 《神农本草经》卷一上经的薏苡仁：味甘微寒，主拘挛不可屈伸、风湿痹、下气。
@@ -624,19 +1383,19 @@
     <t>2026-09-17 19:00:00</t>
   </si>
   <si>
-    <t>2459</t>
-  </si>
-  <si>
-    <t>0.143318</t>
-  </si>
-  <si>
-    <t>0.365588</t>
-  </si>
-  <si>
-    <t>0.267462</t>
-  </si>
-  <si>
-    <t>7.499148</t>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>0.144630</t>
+  </si>
+  <si>
+    <t>0.366543</t>
+  </si>
+  <si>
+    <t>0.268260</t>
+  </si>
+  <si>
+    <t>7.478963</t>
   </si>
   <si>
     <t>署豫：就是后来的山药 《神农本草经》卷一上经的署豫（薯蓣）：味甘温，主伤中、补虚羸、益气力、长肌肉。
@@ -648,19 +1407,19 @@
     <t>2026-09-17 08:00:00</t>
   </si>
   <si>
-    <t>2814</t>
-  </si>
-  <si>
-    <t>0.158355</t>
-  </si>
-  <si>
-    <t>0.400989</t>
-  </si>
-  <si>
-    <t>0.234785</t>
-  </si>
-  <si>
-    <t>7.385542</t>
+    <t>2832</t>
+  </si>
+  <si>
+    <t>0.158827</t>
+  </si>
+  <si>
+    <t>0.402394</t>
+  </si>
+  <si>
+    <t>0.234500</t>
+  </si>
+  <si>
+    <t>7.376611</t>
   </si>
   <si>
     <t>木香：辟毒疫温鬼的本经香药 《神农本草经》卷一上经的木香：味辛，主邪气、辟毒疫温鬼、强志。
@@ -672,19 +1431,19 @@
     <t>2026-09-16 19:00:00</t>
   </si>
   <si>
-    <t>1317</t>
-  </si>
-  <si>
-    <t>0.120344</t>
-  </si>
-  <si>
-    <t>0.307263</t>
-  </si>
-  <si>
-    <t>0.247905</t>
-  </si>
-  <si>
-    <t>5.699022</t>
+    <t>1374</t>
+  </si>
+  <si>
+    <t>0.121233</t>
+  </si>
+  <si>
+    <t>0.305858</t>
+  </si>
+  <si>
+    <t>0.252044</t>
+  </si>
+  <si>
+    <t>5.681199</t>
   </si>
   <si>
     <t>车前子：牛迹里长出的当道草 《神农本草经》卷一上经的车前子：味甘寒，主气癃、利水道小便、除湿痹。
@@ -696,25 +1455,19 @@
     <t>2026-09-16 08:00:00</t>
   </si>
   <si>
-    <t>4862</t>
-  </si>
-  <si>
-    <t>0.210414</t>
-  </si>
-  <si>
-    <t>0.458104</t>
-  </si>
-  <si>
-    <t>0.220057</t>
-  </si>
-  <si>
-    <t>10.188739</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>4884</t>
+  </si>
+  <si>
+    <t>0.210517</t>
+  </si>
+  <si>
+    <t>0.458181</t>
+  </si>
+  <si>
+    <t>0.220378</t>
+  </si>
+  <si>
+    <t>10.172917</t>
   </si>
   <si>
     <t>独活：无风自动的本经上品 《神农本草经》卷一上经的独活：味苦平，主风寒所击、金疮止痛、女子疝瘕。
@@ -726,19 +1479,19 @@
     <t>2026-09-15 20:06:14</t>
   </si>
   <si>
-    <t>2921</t>
-  </si>
-  <si>
-    <t>0.161551</t>
-  </si>
-  <si>
-    <t>0.371713</t>
-  </si>
-  <si>
-    <t>0.274214</t>
-  </si>
-  <si>
-    <t>8.170513</t>
+    <t>2934</t>
+  </si>
+  <si>
+    <t>0.161691</t>
+  </si>
+  <si>
+    <t>0.372687</t>
+  </si>
+  <si>
+    <t>0.274410</t>
+  </si>
+  <si>
+    <t>8.160714</t>
   </si>
   <si>
     <t>麦门冬：别名不死药的润肺上品 《神农本草经》卷一上经的麦门冬：味甘平，主心腹结气、胃络脉绝、羸瘦短气。
@@ -750,19 +1503,16 @@
     <t>2026-09-14 08:00:00</t>
   </si>
   <si>
-    <t>964</t>
-  </si>
-  <si>
-    <t>0.160633</t>
-  </si>
-  <si>
-    <t>0.367412</t>
-  </si>
-  <si>
-    <t>0.302449</t>
-  </si>
-  <si>
-    <t>7.519702</t>
+    <t>0.164080</t>
+  </si>
+  <si>
+    <t>0.367816</t>
+  </si>
+  <si>
+    <t>0.299896</t>
+  </si>
+  <si>
+    <t>7.520376</t>
   </si>
   <si>
     <t>防葵：博物志说它与狼毒相似 《神农本草经》卷一上经的防葵：味辛寒，主疝瘕肠泄、膀胱热结、惊邪狂走。
@@ -774,19 +1524,19 @@
     <t>2026-09-13 20:00:00</t>
   </si>
   <si>
-    <t>4278</t>
-  </si>
-  <si>
-    <t>0.159919</t>
-  </si>
-  <si>
-    <t>0.415624</t>
-  </si>
-  <si>
-    <t>0.190117</t>
-  </si>
-  <si>
-    <t>7.664437</t>
+    <t>4298</t>
+  </si>
+  <si>
+    <t>0.159732</t>
+  </si>
+  <si>
+    <t>0.414096</t>
+  </si>
+  <si>
+    <t>0.190874</t>
+  </si>
+  <si>
+    <t>7.634319</t>
   </si>
   <si>
     <t>女萎：就是后来的玉竹 《神农本草经》卷一上经的女萎：味甘平，主中风暴热、跌筋结肉，久服好颜色。
@@ -798,19 +1548,19 @@
     <t>2026-09-13 08:00:00</t>
   </si>
   <si>
-    <t>3304</t>
-  </si>
-  <si>
-    <t>0.128834</t>
-  </si>
-  <si>
-    <t>0.401658</t>
-  </si>
-  <si>
-    <t>0.181394</t>
-  </si>
-  <si>
-    <t>7.181653</t>
+    <t>3330</t>
+  </si>
+  <si>
+    <t>0.128938</t>
+  </si>
+  <si>
+    <t>0.401903</t>
+  </si>
+  <si>
+    <t>0.182823</t>
+  </si>
+  <si>
+    <t>7.176138</t>
   </si>
   <si>
     <t>充蔚子：本经里的益母草子 《神农本草经》卷一上经的充蔚子（茺蔚子）：味辛微温，主明目益精、除水气，茎可作浴汤。
@@ -822,19 +1572,19 @@
     <t>2026-09-12 19:13:39</t>
   </si>
   <si>
-    <t>761</t>
-  </si>
-  <si>
-    <t>0.148448</t>
-  </si>
-  <si>
-    <t>0.342308</t>
-  </si>
-  <si>
-    <t>0.314103</t>
-  </si>
-  <si>
-    <t>6.982051</t>
+    <t>772</t>
+  </si>
+  <si>
+    <t>0.150266</t>
+  </si>
+  <si>
+    <t>0.342172</t>
+  </si>
+  <si>
+    <t>0.311869</t>
+  </si>
+  <si>
+    <t>6.953283</t>
   </si>
   <si>
     <t>牛膝：陶弘景说它茎像牛膝 《神农本草经》卷一上经的牛膝：味苦酸，主寒湿痿痹、膝痛不可屈伸，逐血气。
@@ -846,19 +1596,19 @@
     <t>2026-08-30 14:00:00</t>
   </si>
   <si>
-    <t>3257</t>
-  </si>
-  <si>
-    <t>0.190182</t>
-  </si>
-  <si>
-    <t>0.422520</t>
-  </si>
-  <si>
-    <t>0.236622</t>
-  </si>
-  <si>
-    <t>8.748049</t>
+    <t>3279</t>
+  </si>
+  <si>
+    <t>0.191353</t>
+  </si>
+  <si>
+    <t>0.423321</t>
+  </si>
+  <si>
+    <t>0.235700</t>
+  </si>
+  <si>
+    <t>8.739431</t>
   </si>
   <si>
     <t>菟丝子：本经续绝伤的上品 《神农本草经》卷一上经的菟丝子：味辛平，主续绝伤、益气力、肥健，汁去面皯。
@@ -870,19 +1620,19 @@
     <t>2026-08-30 08:00:00</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>0.247706</t>
-  </si>
-  <si>
-    <t>0.427481</t>
-  </si>
-  <si>
-    <t>0.236641</t>
-  </si>
-  <si>
-    <t>7.236641</t>
+    <t>122</t>
+  </si>
+  <si>
+    <t>0.241667</t>
+  </si>
+  <si>
+    <t>0.433566</t>
+  </si>
+  <si>
+    <t>0.230769</t>
+  </si>
+  <si>
+    <t>7.041958</t>
   </si>
   <si>
     <t>术：本经里"长服山精"的上品 《神农本草经》卷一上经的术：味苦温，主风寒湿痹、死肌、痉、疸，止汗除热消食。
@@ -894,19 +1644,19 @@
     <t>2026-08-29 14:00:00</t>
   </si>
   <si>
-    <t>2453</t>
-  </si>
-  <si>
-    <t>0.145616</t>
-  </si>
-  <si>
-    <t>0.356241</t>
-  </si>
-  <si>
-    <t>0.254458</t>
-  </si>
-  <si>
-    <t>9.834695</t>
+    <t>2469</t>
+  </si>
+  <si>
+    <t>0.147025</t>
+  </si>
+  <si>
+    <t>0.356695</t>
+  </si>
+  <si>
+    <t>0.254150</t>
+  </si>
+  <si>
+    <t>9.842125</t>
   </si>
   <si>
     <t>干地黄：本经"填骨髓"的第一补药 《神农本草经》卷一上经的干地黄：味甘寒，主折跌绝筋、逐血痹、填骨髓，生者尤良。
@@ -918,19 +1668,19 @@
     <t>2026-08-29 08:00:00</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>0.276923</t>
-  </si>
-  <si>
-    <t>0.375000</t>
-  </si>
-  <si>
-    <t>0.312500</t>
-  </si>
-  <si>
-    <t>6.925000</t>
+    <t>83</t>
+  </si>
+  <si>
+    <t>0.273973</t>
+  </si>
+  <si>
+    <t>0.395604</t>
+  </si>
+  <si>
+    <t>0.296703</t>
+  </si>
+  <si>
+    <t>7.186813</t>
   </si>
   <si>
     <t>天门冬：抱朴子也记了它一堆别名 《神农本草经》卷一上经的天门冬：味苦平，主诸暴风湿偏痹，强骨髓，杀三虫。
@@ -942,19 +1692,19 @@
     <t>2026-08-28 08:00:00</t>
   </si>
   <si>
-    <t>1865</t>
-  </si>
-  <si>
-    <t>0.143832</t>
-  </si>
-  <si>
-    <t>0.361238</t>
-  </si>
-  <si>
-    <t>0.284627</t>
-  </si>
-  <si>
-    <t>7.365063</t>
+    <t>1885</t>
+  </si>
+  <si>
+    <t>0.144723</t>
+  </si>
+  <si>
+    <t>0.361069</t>
+  </si>
+  <si>
+    <t>0.283409</t>
+  </si>
+  <si>
+    <t>7.364368</t>
   </si>
   <si>
     <t>鞠华：本经里"目欲脱"的菊花 《神农本草经》卷一上经的鞠华（菊花）：味苦平，主风、头眩肿痛、目欲脱、泪出，久服耐老延年。
@@ -966,19 +1716,19 @@
     <t>2026-08-27 14:00:00</t>
   </si>
   <si>
-    <t>534</t>
-  </si>
-  <si>
-    <t>0.116071</t>
-  </si>
-  <si>
-    <t>0.302048</t>
-  </si>
-  <si>
-    <t>0.322526</t>
-  </si>
-  <si>
-    <t>5.721843</t>
+    <t>542</t>
+  </si>
+  <si>
+    <t>0.118375</t>
+  </si>
+  <si>
+    <t>0.302365</t>
+  </si>
+  <si>
+    <t>0.322635</t>
+  </si>
+  <si>
+    <t>5.724662</t>
   </si>
   <si>
     <t>菖蒲：通九窍、明耳目的本经上品 《神农本草经》卷一上经的菖蒲：味辛温，主风寒湿痹、咳逆上气，开心孔，通九窍，明耳目。
@@ -990,19 +1740,19 @@
     <t>2026-08-27 08:00:00</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>0.141956</t>
-  </si>
-  <si>
-    <t>0.337143</t>
-  </si>
-  <si>
-    <t>0.354286</t>
-  </si>
-  <si>
-    <t>5.837143</t>
+    <t>330</t>
+  </si>
+  <si>
+    <t>0.145511</t>
+  </si>
+  <si>
+    <t>0.337989</t>
+  </si>
+  <si>
+    <t>0.349162</t>
+  </si>
+  <si>
+    <t>5.810056</t>
   </si>
   <si>
     <t>扁青：本经主折跌痈肿 《神农本草经》里的扁青：味甘平，主目痛、折跌、痈肿、金创不疗，利精神。
@@ -1014,19 +1764,19 @@
     <t>2026-08-26 14:00:00</t>
   </si>
   <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>0.127389</t>
-  </si>
-  <si>
-    <t>0.247059</t>
-  </si>
-  <si>
-    <t>0.382353</t>
-  </si>
-  <si>
-    <t>7.688235</t>
+    <t>209</t>
+  </si>
+  <si>
+    <t>0.138614</t>
+  </si>
+  <si>
+    <t>0.283105</t>
+  </si>
+  <si>
+    <t>0.360731</t>
+  </si>
+  <si>
+    <t>7.269406</t>
   </si>
   <si>
     <t>白青：可消而为铜的本经石药 《神农本草经》里的白青：味甘平，主明目、利九窍、耳聋，杀诸毒、三虫。
@@ -1038,19 +1788,19 @@
     <t>2026-08-26 08:00:00</t>
   </si>
   <si>
-    <t>632</t>
-  </si>
-  <si>
-    <t>0.152466</t>
-  </si>
-  <si>
-    <t>0.350000</t>
-  </si>
-  <si>
-    <t>0.251429</t>
-  </si>
-  <si>
-    <t>11.078571</t>
+    <t>643</t>
+  </si>
+  <si>
+    <t>0.152493</t>
+  </si>
+  <si>
+    <t>0.349229</t>
+  </si>
+  <si>
+    <t>0.258065</t>
+  </si>
+  <si>
+    <t>10.946704</t>
   </si>
   <si>
     <t>紫石英：绝孕十年无子的本经说法 《神农本草经》里的紫石英：味甘温，主心腹咳逆，补不足，有女子风寒在子宫的古说。
@@ -1062,22 +1812,22 @@
     <t>2026-08-23 20:35:00</t>
   </si>
   <si>
-    <t>4621</t>
-  </si>
-  <si>
-    <t>0.115930</t>
-  </si>
-  <si>
-    <t>0.355032</t>
-  </si>
-  <si>
-    <t>0.226038</t>
-  </si>
-  <si>
-    <t>7.086861</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>4669</t>
+  </si>
+  <si>
+    <t>0.116650</t>
+  </si>
+  <si>
+    <t>0.355151</t>
+  </si>
+  <si>
+    <t>0.226023</t>
+  </si>
+  <si>
+    <t>7.090765</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>白石英：本经主消渴阴痿 《神农本草经》里的白石英：味甘微温，主消渴、阴痿不足、胸膈间久寒，益气。
@@ -1089,22 +1839,19 @@
     <t>2026-08-23 18:32:24</t>
   </si>
   <si>
-    <t>3629</t>
-  </si>
-  <si>
-    <t>0.101398</t>
-  </si>
-  <si>
-    <t>0.331879</t>
-  </si>
-  <si>
-    <t>0.260908</t>
-  </si>
-  <si>
-    <t>5.680628</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>3685</t>
+  </si>
+  <si>
+    <t>0.102196</t>
+  </si>
+  <si>
+    <t>0.332193</t>
+  </si>
+  <si>
+    <t>0.261192</t>
+  </si>
+  <si>
+    <t>5.678643</t>
   </si>
   <si>
     <t>太乙余食：一名石脑的本经石药 《神农本草经》里的太乙余食：味甘平，主咳逆上气、症瘕血闭漏下，一名石脑。
@@ -1116,19 +1863,19 @@
     <t>2026-08-22 14:50:00</t>
   </si>
   <si>
-    <t>1567</t>
-  </si>
-  <si>
-    <t>0.126000</t>
-  </si>
-  <si>
-    <t>0.397953</t>
-  </si>
-  <si>
-    <t>0.247601</t>
-  </si>
-  <si>
-    <t>7.589891</t>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>0.127632</t>
+  </si>
+  <si>
+    <t>0.397606</t>
+  </si>
+  <si>
+    <t>0.247007</t>
+  </si>
+  <si>
+    <t>7.556396</t>
   </si>
   <si>
     <t>禹余粮：名字从大禹治水来 《神农本草经》里的禹余粮：味甘寒，主咳逆、寒热烦满、血闭症瘕。
@@ -1140,19 +1887,19 @@
     <t>2026-08-22 10:39:43</t>
   </si>
   <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>0.139908</t>
-  </si>
-  <si>
-    <t>0.326964</t>
-  </si>
-  <si>
-    <t>0.307856</t>
-  </si>
-  <si>
-    <t>5.878981</t>
+    <t>505</t>
+  </si>
+  <si>
+    <t>0.145374</t>
+  </si>
+  <si>
+    <t>0.330629</t>
+  </si>
+  <si>
+    <t>0.312373</t>
+  </si>
+  <si>
+    <t>5.922921</t>
   </si>
   <si>
     <t>曾青：铜之精的本经石药 《神农本草经》里的曾青：味酸小寒，主目痛止泪，破症坚积聚，久服轻身。
@@ -1164,19 +1911,19 @@
     <t>2026-08-21 20:00:00</t>
   </si>
   <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>0.083333</t>
-  </si>
-  <si>
-    <t>0.294118</t>
-  </si>
-  <si>
-    <t>0.400000</t>
-  </si>
-  <si>
-    <t>4.388235</t>
+    <t>96</t>
+  </si>
+  <si>
+    <t>0.094737</t>
+  </si>
+  <si>
+    <t>0.291667</t>
+  </si>
+  <si>
+    <t>0.395833</t>
+  </si>
+  <si>
+    <t>4.385417</t>
   </si>
   <si>
     <t>空青：能化铜铁铅锡作金 《神农本草经》里的空青：味甘寒，主眚盲耳聋，通血脉，养精神，能化铜铁铅锡作金。
@@ -1188,19 +1935,19 @@
     <t>2026-08-21 09:52:17</t>
   </si>
   <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>0.155629</t>
-  </si>
-  <si>
-    <t>0.346032</t>
-  </si>
-  <si>
-    <t>0.288889</t>
-  </si>
-  <si>
-    <t>6.857143</t>
+    <t>300</t>
+  </si>
+  <si>
+    <t>0.160772</t>
+  </si>
+  <si>
+    <t>0.342424</t>
+  </si>
+  <si>
+    <t>0.287879</t>
+  </si>
+  <si>
+    <t>6.733333</t>
   </si>
   <si>
     <t>滑石：利小便的本经石药 《神农本草经》里的滑石：味甘寒，主身热泄、女子乳难、癃闭，利小便，益精气。
@@ -1212,22 +1959,19 @@
     <t>2026-08-19 09:14:26</t>
   </si>
   <si>
-    <t>851</t>
-  </si>
-  <si>
-    <t>0.115099</t>
-  </si>
-  <si>
-    <t>0.281657</t>
-  </si>
-  <si>
-    <t>0.349112</t>
-  </si>
-  <si>
-    <t>5.514793</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>859</t>
+  </si>
+  <si>
+    <t>0.116851</t>
+  </si>
+  <si>
+    <t>0.282021</t>
+  </si>
+  <si>
+    <t>0.347826</t>
+  </si>
+  <si>
+    <t>5.513514</t>
   </si>
   <si>
     <t>朴硝：能化七十二种石 《神农本草经》里的朴硝：味苦寒，逐六腑积聚，结固留癖，能化七十二种石。
@@ -1239,19 +1983,16 @@
     <t>2026-08-18 20:00:00</t>
   </si>
   <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>0.119403</t>
-  </si>
-  <si>
-    <t>0.276596</t>
-  </si>
-  <si>
-    <t>0.297872</t>
-  </si>
-  <si>
-    <t>5.319149</t>
+    <t>148</t>
+  </si>
+  <si>
+    <t>0.127517</t>
+  </si>
+  <si>
+    <t>0.292994</t>
+  </si>
+  <si>
+    <t>6.471338</t>
   </si>
   <si>
     <t>硝石：本经主五脏积热 《神农本草经》里的硝石：味苦寒，主五脏积热，涤去蓄结饮食，推陈致新。
@@ -1263,19 +2004,19 @@
     <t>2026-08-18 09:08:09</t>
   </si>
   <si>
-    <t>3261</t>
-  </si>
-  <si>
-    <t>0.135716</t>
-  </si>
-  <si>
-    <t>0.379320</t>
-  </si>
-  <si>
-    <t>0.236087</t>
-  </si>
-  <si>
-    <t>7.120387</t>
+    <t>3287</t>
+  </si>
+  <si>
+    <t>0.136022</t>
+  </si>
+  <si>
+    <t>0.379110</t>
+  </si>
+  <si>
+    <t>0.236253</t>
+  </si>
+  <si>
+    <t>7.105906</t>
   </si>
   <si>
     <t>涅石：本经里的明矾石 《神农本草经》卷一上经的干地黄：味甘寒，主折跌绝筋、逐血痹、填骨髓，生者尤良。
@@ -1287,19 +2028,19 @@
     <t>2026-08-17 10:01:55</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>0.159574</t>
-  </si>
-  <si>
-    <t>0.257732</t>
-  </si>
-  <si>
-    <t>0.381443</t>
-  </si>
-  <si>
-    <t>4.793814</t>
+    <t>106</t>
+  </si>
+  <si>
+    <t>0.171717</t>
+  </si>
+  <si>
+    <t>0.274510</t>
+  </si>
+  <si>
+    <t>0.372549</t>
+  </si>
+  <si>
+    <t>4.892157</t>
   </si>
   <si>
     <t>石钟乳：溶洞钟乳也是本草 《神农本草经》里的石钟乳：味甘温，主咳逆上气，通百节，利九窍，下乳汁。
@@ -1311,19 +2052,19 @@
     <t>2026-08-16 08:26:56</t>
   </si>
   <si>
-    <t>932</t>
-  </si>
-  <si>
-    <t>0.107791</t>
-  </si>
-  <si>
-    <t>0.286294</t>
-  </si>
-  <si>
-    <t>0.330964</t>
-  </si>
-  <si>
-    <t>5.026396</t>
+    <t>952</t>
+  </si>
+  <si>
+    <t>0.111462</t>
+  </si>
+  <si>
+    <t>0.287276</t>
+  </si>
+  <si>
+    <t>0.329026</t>
+  </si>
+  <si>
+    <t>5.050696</t>
   </si>
   <si>
     <t>玉泉：食玉之说从何而来 《神农本草经》里的玉泉（玉）：味甘平，主柔筋强骨、安魂魄、长肌肉，久服耐寒暑。
@@ -1335,19 +2076,19 @@
     <t>2026-08-15 09:43:06</t>
   </si>
   <si>
-    <t>1261</t>
-  </si>
-  <si>
-    <t>0.105605</t>
-  </si>
-  <si>
-    <t>0.240563</t>
-  </si>
-  <si>
-    <t>0.396743</t>
-  </si>
-  <si>
-    <t>5.233901</t>
+    <t>1279</t>
+  </si>
+  <si>
+    <t>0.108347</t>
+  </si>
+  <si>
+    <t>0.245985</t>
+  </si>
+  <si>
+    <t>0.393431</t>
+  </si>
+  <si>
+    <t>5.284672</t>
   </si>
   <si>
     <t>云母：六个别名的本经上品 《神农本草经》卷一石部之首的云母：味甘平，主身皮死肌、安五脏、益子精、明目。
@@ -1359,19 +2100,19 @@
     <t>2026-08-14 10:38:46</t>
   </si>
   <si>
-    <t>594</t>
-  </si>
-  <si>
-    <t>0.131810</t>
-  </si>
-  <si>
-    <t>0.271565</t>
-  </si>
-  <si>
-    <t>0.359425</t>
-  </si>
-  <si>
-    <t>4.748006</t>
+    <t>605</t>
+  </si>
+  <si>
+    <t>0.134251</t>
+  </si>
+  <si>
+    <t>0.270736</t>
+  </si>
+  <si>
+    <t>0.353678</t>
+  </si>
+  <si>
+    <t>4.748437</t>
   </si>
   <si>
     <t>丹沙：能化为汞的本经石药 《神农本草经》卷一开篇第一味药是丹沙（朱砂）：味甘微寒，养精神，安魂魄，明目。
@@ -1383,19 +2124,19 @@
     <t>2026-08-14 10:24:41</t>
   </si>
   <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>0.115385</t>
-  </si>
-  <si>
-    <t>0.253012</t>
-  </si>
-  <si>
-    <t>0.403614</t>
-  </si>
-  <si>
-    <t>5.210843</t>
+    <t>177</t>
+  </si>
+  <si>
+    <t>0.125000</t>
+  </si>
+  <si>
+    <t>0.264865</t>
+  </si>
+  <si>
+    <t>0.389189</t>
+  </si>
+  <si>
+    <t>5.243243</t>
   </si>
   <si>
     <t>黄耆：痈疽 排脓 小儿百病 《神农本草经》里的黄耆：味甘，微温，主治痈疽久败创、排脓止痛，又补虚、治小儿百病；别名戴糁，生于山谷，二月、十月采。
@@ -1406,19 +2147,19 @@
     <t>2026-08-14 10:18:02</t>
   </si>
   <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>0.104575</t>
-  </si>
-  <si>
-    <t>0.288854</t>
-  </si>
-  <si>
-    <t>0.357928</t>
-  </si>
-  <si>
-    <t>4.653061</t>
+    <t>661</t>
+  </si>
+  <si>
+    <t>0.113744</t>
+  </si>
+  <si>
+    <t>0.299094</t>
+  </si>
+  <si>
+    <t>0.347432</t>
+  </si>
+  <si>
+    <t>4.773414</t>
   </si>
   <si>
     <t>甘草：古书里写了什么？ 《神农本草经》如何记载甘草？
@@ -1430,19 +2171,19 @@
     <t>2026-08-12 10:38:33</t>
   </si>
   <si>
-    <t>812</t>
-  </si>
-  <si>
-    <t>0.213439</t>
-  </si>
-  <si>
-    <t>0.250301</t>
-  </si>
-  <si>
-    <t>0.377858</t>
-  </si>
-  <si>
-    <t>5.599278</t>
+    <t>835</t>
+  </si>
+  <si>
+    <t>0.226923</t>
+  </si>
+  <si>
+    <t>0.261430</t>
+  </si>
+  <si>
+    <t>0.371630</t>
+  </si>
+  <si>
+    <t>5.676436</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +2550,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -1924,18 +2665,18 @@
         <v>28</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -1944,48 +2685,48 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1994,48 +2735,48 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -2044,48 +2785,48 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="L5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -2094,98 +2835,98 @@
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -2194,48 +2935,48 @@
         <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -2244,48 +2985,48 @@
         <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -2294,48 +3035,48 @@
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="P10" s="1" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -2344,48 +3085,48 @@
         <v>19</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
@@ -2394,48 +3135,48 @@
         <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -2444,48 +3185,48 @@
         <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>18</v>
@@ -2494,48 +3235,48 @@
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
@@ -2544,48 +3285,48 @@
         <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -2594,48 +3335,48 @@
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="O16" s="1" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
@@ -2644,48 +3385,48 @@
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -2694,48 +3435,48 @@
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
@@ -2744,48 +3485,48 @@
         <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
@@ -2794,48 +3535,48 @@
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
@@ -2844,48 +3585,48 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
@@ -2894,37 +3635,37 @@
         <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>27</v>
@@ -2932,10 +3673,10 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
@@ -2944,48 +3685,48 @@
         <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
@@ -2994,48 +3735,48 @@
         <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="O24" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
@@ -3044,48 +3785,48 @@
         <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
@@ -3094,48 +3835,48 @@
         <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
@@ -3144,48 +3885,48 @@
         <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -3194,48 +3935,48 @@
         <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="L28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="P28" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -3244,48 +3985,48 @@
         <v>19</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -3294,48 +4035,48 @@
         <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
@@ -3344,48 +4085,48 @@
         <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>18</v>
@@ -3394,48 +4135,48 @@
         <v>19</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
@@ -3444,48 +4185,48 @@
         <v>19</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -3494,48 +4235,48 @@
         <v>19</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="P34" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -3544,48 +4285,48 @@
         <v>19</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
@@ -3594,48 +4335,48 @@
         <v>19</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
@@ -3644,48 +4385,48 @@
         <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
@@ -3694,48 +4435,48 @@
         <v>19</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="K38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
@@ -3744,48 +4485,48 @@
         <v>19</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>18</v>
@@ -3794,48 +4535,48 @@
         <v>19</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>314</v>
+        <v>104</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P40" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>18</v>
@@ -3844,48 +4585,48 @@
         <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>322</v>
+        <v>149</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>18</v>
@@ -3894,48 +4635,48 @@
         <v>19</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -3944,37 +4685,37 @@
         <v>19</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>37</v>
+        <v>348</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>38</v>
@@ -3982,10 +4723,10 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -3994,48 +4735,48 @@
         <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>27</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>18</v>
@@ -4044,48 +4785,48 @@
         <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>18</v>
@@ -4094,48 +4835,48 @@
         <v>19</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>358</v>
+        <v>95</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>18</v>
@@ -4144,48 +4885,48 @@
         <v>19</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>361</v>
+        <v>280</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>18</v>
@@ -4194,48 +4935,48 @@
         <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>18</v>
@@ -4244,48 +4985,48 @@
         <v>19</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>18</v>
@@ -4294,48 +5035,48 @@
         <v>19</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>208</v>
+        <v>38</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M50" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>18</v>
@@ -4344,48 +5085,48 @@
         <v>19</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>314</v>
+        <v>104</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>18</v>
@@ -4394,48 +5135,48 @@
         <v>19</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>18</v>
@@ -4444,48 +5185,48 @@
         <v>19</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>47</v>
+        <v>348</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>38</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>18</v>
@@ -4494,48 +5235,48 @@
         <v>19</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>18</v>
@@ -4544,40 +5285,1390 @@
         <v>19</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="L55" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O59" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="P59" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N55" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O55" s="1" t="s">
+      <c r="L61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>38</v>
+      <c r="L79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
